--- a/lang/ko/headTags.xlsx
+++ b/lang/ko/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1178</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2259">
   <si>
     <t>en</t>
   </si>
@@ -6361,424 +6361,427 @@
     <t>트위스티드 원더랜드</t>
   </si>
   <si>
+    <t>ULTRAKILL</t>
+  </si>
+  <si>
+    <t>울트라킬</t>
+  </si>
+  <si>
+    <t>Umineko - When They Cry</t>
+  </si>
+  <si>
+    <t>우미네코 - 그들이 울 때</t>
+  </si>
+  <si>
+    <t>Undertale</t>
+  </si>
+  <si>
+    <t>언더테일</t>
+  </si>
+  <si>
+    <t>Undertale AU</t>
+  </si>
+  <si>
+    <t>언더테일 AU</t>
+  </si>
+  <si>
+    <t>Undertale Yellow</t>
+  </si>
+  <si>
+    <t>언더테일 옐로우</t>
+  </si>
+  <si>
+    <t>Universal Symbol</t>
+  </si>
+  <si>
+    <t>범용 기호</t>
+  </si>
+  <si>
+    <t>Up</t>
+  </si>
+  <si>
+    <t>Urban Wildlife</t>
+  </si>
+  <si>
+    <t>도시 야생동물</t>
+  </si>
+  <si>
+    <t>V for Vendetta</t>
+  </si>
+  <si>
+    <t>브이 포 벤데타</t>
+  </si>
+  <si>
+    <t>Valentines</t>
+  </si>
+  <si>
+    <t>발렌타인</t>
+  </si>
+  <si>
+    <t>Valorant</t>
+  </si>
+  <si>
+    <t>용맹한</t>
+  </si>
+  <si>
+    <t>Vanilla (removed)</t>
+  </si>
+  <si>
+    <t>바닐라 (제거됨)</t>
+  </si>
+  <si>
+    <t>Vanilla Block</t>
+  </si>
+  <si>
+    <t>바닐라 블록</t>
+  </si>
+  <si>
+    <t>Vanilla Food</t>
+  </si>
+  <si>
+    <t>바닐라 음식</t>
+  </si>
+  <si>
+    <t>Vanilla Helmet</t>
+  </si>
+  <si>
+    <t>바닐라 헬멧</t>
+  </si>
+  <si>
+    <t>Vanilla Item</t>
+  </si>
+  <si>
+    <t>바닐라 아이템</t>
+  </si>
+  <si>
+    <t>Vanilla Mob</t>
+  </si>
+  <si>
+    <t>바닐라 몹</t>
+  </si>
+  <si>
+    <t>Vault Hunters</t>
+  </si>
+  <si>
+    <t>볼트 헌터</t>
+  </si>
+  <si>
+    <t>Vegetable</t>
+  </si>
+  <si>
+    <t>야채</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>차량</t>
+  </si>
+  <si>
+    <t>Vikings</t>
+  </si>
+  <si>
+    <t>바이킹</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>마을 주민</t>
+  </si>
+  <si>
+    <t>Villager (Desert)</t>
+  </si>
+  <si>
+    <t>마을 주민(사막)</t>
+  </si>
+  <si>
+    <t>Villager (Jungle)</t>
+  </si>
+  <si>
+    <t>마을 주민(정글)</t>
+  </si>
+  <si>
+    <t>Villager (Plains)</t>
+  </si>
+  <si>
+    <t>마을 주민(평원)</t>
+  </si>
+  <si>
+    <t>Villager (Savanna)</t>
+  </si>
+  <si>
+    <t>마을 주민(사바나)</t>
+  </si>
+  <si>
+    <t>Villager (Snowy Tundra)</t>
+  </si>
+  <si>
+    <t>마을 주민(설원의 툰드라)</t>
+  </si>
+  <si>
+    <t>Villager (Swamp)</t>
+  </si>
+  <si>
+    <t>마을 주민(늪지대)</t>
+  </si>
+  <si>
+    <t>Villager (Taiga)</t>
+  </si>
+  <si>
+    <t>마을 주민(타이가)</t>
+  </si>
+  <si>
+    <t>Virtual Youtuber</t>
+  </si>
+  <si>
+    <t>가상 유튜버</t>
+  </si>
+  <si>
+    <t>Vocaloid</t>
+  </si>
+  <si>
+    <t>보컬로이드</t>
+  </si>
+  <si>
+    <t>Voltron</t>
+  </si>
+  <si>
+    <t>볼트론</t>
+  </si>
+  <si>
+    <t>Wakfu</t>
+  </si>
+  <si>
+    <t>왁푸</t>
+  </si>
+  <si>
+    <t>Walking Dead</t>
+  </si>
+  <si>
+    <t>워킹 데드</t>
+  </si>
+  <si>
+    <t>Wall-E</t>
+  </si>
+  <si>
+    <t>Wallace and Gromit</t>
+  </si>
+  <si>
+    <t>월레스와 그로밋</t>
+  </si>
+  <si>
+    <t>War of the Worlds</t>
+  </si>
+  <si>
+    <t>세계의 전쟁</t>
+  </si>
+  <si>
+    <t>Warcraft</t>
+  </si>
+  <si>
+    <t>워크래프트</t>
+  </si>
+  <si>
+    <t>Warframe</t>
+  </si>
+  <si>
+    <t>워프레임</t>
+  </si>
+  <si>
+    <t>Warhammer</t>
+  </si>
+  <si>
+    <t>워해머</t>
+  </si>
+  <si>
+    <t>Warrior Cats</t>
+  </si>
+  <si>
+    <t>전사 고양이</t>
+  </si>
+  <si>
+    <t>We Bear Bears</t>
+  </si>
+  <si>
+    <t>위 베어 베어스</t>
+  </si>
+  <si>
+    <t>We Happy Few</t>
+  </si>
+  <si>
+    <t>우리 행복한 소수</t>
+  </si>
+  <si>
+    <t>Weather</t>
+  </si>
+  <si>
+    <t>날씨</t>
+  </si>
+  <si>
+    <t>Welcome Home</t>
+  </si>
+  <si>
+    <t>웰컴 홈</t>
+  </si>
+  <si>
+    <t>Who is this?</t>
+  </si>
+  <si>
+    <t>누구세요?</t>
+  </si>
+  <si>
+    <t>Wild Update</t>
+  </si>
+  <si>
+    <t>와일드 업데이트</t>
+  </si>
+  <si>
+    <t>Wings of Fire</t>
+  </si>
+  <si>
+    <t>불의 날개</t>
+  </si>
+  <si>
+    <t>Winnie the Pooh</t>
+  </si>
+  <si>
+    <t>곰돌이 푸</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>겨울</t>
+  </si>
+  <si>
+    <t>Witcher</t>
+  </si>
+  <si>
+    <t>Wonderful Wonder World</t>
+  </si>
+  <si>
+    <t>원더 원더 월드</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>목재</t>
+  </si>
+  <si>
+    <t>Wool</t>
+  </si>
+  <si>
+    <t>Work Safety Helmet</t>
+  </si>
+  <si>
+    <t>작업 안전 헬멧</t>
+  </si>
+  <si>
+    <t>Wreck It Ralph</t>
+  </si>
+  <si>
+    <t>주먹왕 랄프</t>
+  </si>
+  <si>
+    <t>Wybel</t>
+  </si>
+  <si>
+    <t>Wynncraft</t>
+  </si>
+  <si>
+    <t>윈크래프트</t>
+  </si>
+  <si>
+    <t>X-Men</t>
+  </si>
+  <si>
+    <t>Xenoblade Chronicles</t>
+  </si>
+  <si>
+    <t>제노블레이드 크로니클</t>
+  </si>
+  <si>
+    <t>Yandere Simulator</t>
+  </si>
+  <si>
+    <t>얀데레 시뮬레이터</t>
+  </si>
+  <si>
+    <t>Yellow Submarine</t>
+  </si>
+  <si>
+    <t>노란 잠수함</t>
+  </si>
+  <si>
+    <t>Yokai</t>
+  </si>
+  <si>
+    <t>요괴</t>
+  </si>
+  <si>
+    <t>Yooka Laylee</t>
+  </si>
+  <si>
+    <t>유카 레이리</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>Youtube</t>
+  </si>
+  <si>
+    <t>유튜브</t>
+  </si>
+  <si>
+    <t>Yu-Gi-Oh</t>
+  </si>
+  <si>
+    <t>Yume Nikki</t>
+  </si>
+  <si>
+    <t>유메 니키</t>
+  </si>
+  <si>
+    <t>Zero no Tsukaima</t>
+  </si>
+  <si>
+    <t>제로 노 쓰카이마</t>
+  </si>
+  <si>
+    <t>Zero Wing</t>
+  </si>
+  <si>
+    <t>제로 윙</t>
+  </si>
+  <si>
+    <t>Zodiac Sign</t>
+  </si>
+  <si>
+    <t>조디악 표지판</t>
+  </si>
+  <si>
+    <t>Zombie</t>
+  </si>
+  <si>
+    <t>좀비</t>
+  </si>
+  <si>
+    <t>Zombie (Vanilla)</t>
+  </si>
+  <si>
+    <t>좀비 (바닐라)</t>
+  </si>
+  <si>
+    <t>Zootopia</t>
+  </si>
+  <si>
+    <t>주토피아</t>
+  </si>
+  <si>
     <t>Ultrakill</t>
-  </si>
-  <si>
-    <t>울트라킬</t>
-  </si>
-  <si>
-    <t>Umineko - When They Cry</t>
-  </si>
-  <si>
-    <t>우미네코 - 그들이 울 때</t>
-  </si>
-  <si>
-    <t>Undertale</t>
-  </si>
-  <si>
-    <t>언더테일</t>
-  </si>
-  <si>
-    <t>Undertale AU</t>
-  </si>
-  <si>
-    <t>언더테일 AU</t>
-  </si>
-  <si>
-    <t>Undertale Yellow</t>
-  </si>
-  <si>
-    <t>언더테일 옐로우</t>
-  </si>
-  <si>
-    <t>Universal Symbol</t>
-  </si>
-  <si>
-    <t>범용 기호</t>
-  </si>
-  <si>
-    <t>Up</t>
-  </si>
-  <si>
-    <t>Urban Wildlife</t>
-  </si>
-  <si>
-    <t>도시 야생동물</t>
-  </si>
-  <si>
-    <t>V for Vendetta</t>
-  </si>
-  <si>
-    <t>브이 포 벤데타</t>
-  </si>
-  <si>
-    <t>Valentines</t>
-  </si>
-  <si>
-    <t>발렌타인</t>
-  </si>
-  <si>
-    <t>Valorant</t>
-  </si>
-  <si>
-    <t>용맹한</t>
-  </si>
-  <si>
-    <t>Vanilla (removed)</t>
-  </si>
-  <si>
-    <t>바닐라 (제거됨)</t>
-  </si>
-  <si>
-    <t>Vanilla Block</t>
-  </si>
-  <si>
-    <t>바닐라 블록</t>
-  </si>
-  <si>
-    <t>Vanilla Food</t>
-  </si>
-  <si>
-    <t>바닐라 음식</t>
-  </si>
-  <si>
-    <t>Vanilla Helmet</t>
-  </si>
-  <si>
-    <t>바닐라 헬멧</t>
-  </si>
-  <si>
-    <t>Vanilla Item</t>
-  </si>
-  <si>
-    <t>바닐라 아이템</t>
-  </si>
-  <si>
-    <t>Vanilla Mob</t>
-  </si>
-  <si>
-    <t>바닐라 몹</t>
-  </si>
-  <si>
-    <t>Vault Hunters</t>
-  </si>
-  <si>
-    <t>볼트 헌터</t>
-  </si>
-  <si>
-    <t>Vegetable</t>
-  </si>
-  <si>
-    <t>야채</t>
-  </si>
-  <si>
-    <t>Vehicle</t>
-  </si>
-  <si>
-    <t>차량</t>
-  </si>
-  <si>
-    <t>Vikings</t>
-  </si>
-  <si>
-    <t>바이킹</t>
-  </si>
-  <si>
-    <t>Villager</t>
-  </si>
-  <si>
-    <t>마을 주민</t>
-  </si>
-  <si>
-    <t>Villager (Desert)</t>
-  </si>
-  <si>
-    <t>마을 주민(사막)</t>
-  </si>
-  <si>
-    <t>Villager (Jungle)</t>
-  </si>
-  <si>
-    <t>마을 주민(정글)</t>
-  </si>
-  <si>
-    <t>Villager (Plains)</t>
-  </si>
-  <si>
-    <t>마을 주민(평원)</t>
-  </si>
-  <si>
-    <t>Villager (Savanna)</t>
-  </si>
-  <si>
-    <t>마을 주민(사바나)</t>
-  </si>
-  <si>
-    <t>Villager (Snowy Tundra)</t>
-  </si>
-  <si>
-    <t>마을 주민(설원의 툰드라)</t>
-  </si>
-  <si>
-    <t>Villager (Swamp)</t>
-  </si>
-  <si>
-    <t>마을 주민(늪지대)</t>
-  </si>
-  <si>
-    <t>Villager (Taiga)</t>
-  </si>
-  <si>
-    <t>마을 주민(타이가)</t>
-  </si>
-  <si>
-    <t>Virtual Youtuber</t>
-  </si>
-  <si>
-    <t>가상 유튜버</t>
-  </si>
-  <si>
-    <t>Vocaloid</t>
-  </si>
-  <si>
-    <t>보컬로이드</t>
-  </si>
-  <si>
-    <t>Voltron</t>
-  </si>
-  <si>
-    <t>볼트론</t>
-  </si>
-  <si>
-    <t>Wakfu</t>
-  </si>
-  <si>
-    <t>왁푸</t>
-  </si>
-  <si>
-    <t>Walking Dead</t>
-  </si>
-  <si>
-    <t>워킹 데드</t>
-  </si>
-  <si>
-    <t>Wall-E</t>
-  </si>
-  <si>
-    <t>Wallace and Gromit</t>
-  </si>
-  <si>
-    <t>월레스와 그로밋</t>
-  </si>
-  <si>
-    <t>War of the Worlds</t>
-  </si>
-  <si>
-    <t>세계의 전쟁</t>
-  </si>
-  <si>
-    <t>Warcraft</t>
-  </si>
-  <si>
-    <t>워크래프트</t>
-  </si>
-  <si>
-    <t>Warframe</t>
-  </si>
-  <si>
-    <t>워프레임</t>
-  </si>
-  <si>
-    <t>Warhammer</t>
-  </si>
-  <si>
-    <t>워해머</t>
-  </si>
-  <si>
-    <t>Warrior Cats</t>
-  </si>
-  <si>
-    <t>전사 고양이</t>
-  </si>
-  <si>
-    <t>We Bear Bears</t>
-  </si>
-  <si>
-    <t>위 베어 베어스</t>
-  </si>
-  <si>
-    <t>We Happy Few</t>
-  </si>
-  <si>
-    <t>우리 행복한 소수</t>
-  </si>
-  <si>
-    <t>Weather</t>
-  </si>
-  <si>
-    <t>날씨</t>
-  </si>
-  <si>
-    <t>Welcome Home</t>
-  </si>
-  <si>
-    <t>웰컴 홈</t>
-  </si>
-  <si>
-    <t>Who is this?</t>
-  </si>
-  <si>
-    <t>누구세요?</t>
-  </si>
-  <si>
-    <t>Wild Update</t>
-  </si>
-  <si>
-    <t>와일드 업데이트</t>
-  </si>
-  <si>
-    <t>Wings of Fire</t>
-  </si>
-  <si>
-    <t>불의 날개</t>
-  </si>
-  <si>
-    <t>Winnie the Pooh</t>
-  </si>
-  <si>
-    <t>곰돌이 푸</t>
-  </si>
-  <si>
-    <t>Winter</t>
-  </si>
-  <si>
-    <t>겨울</t>
-  </si>
-  <si>
-    <t>Witcher</t>
-  </si>
-  <si>
-    <t>Wonderful Wonder World</t>
-  </si>
-  <si>
-    <t>원더 원더 월드</t>
-  </si>
-  <si>
-    <t>Wood</t>
-  </si>
-  <si>
-    <t>목재</t>
-  </si>
-  <si>
-    <t>Wool</t>
-  </si>
-  <si>
-    <t>Work Safety Helmet</t>
-  </si>
-  <si>
-    <t>작업 안전 헬멧</t>
-  </si>
-  <si>
-    <t>Wreck It Ralph</t>
-  </si>
-  <si>
-    <t>주먹왕 랄프</t>
-  </si>
-  <si>
-    <t>Wybel</t>
-  </si>
-  <si>
-    <t>Wynncraft</t>
-  </si>
-  <si>
-    <t>윈크래프트</t>
-  </si>
-  <si>
-    <t>X-Men</t>
-  </si>
-  <si>
-    <t>Xenoblade Chronicles</t>
-  </si>
-  <si>
-    <t>제노블레이드 크로니클</t>
-  </si>
-  <si>
-    <t>Yandere Simulator</t>
-  </si>
-  <si>
-    <t>얀데레 시뮬레이터</t>
-  </si>
-  <si>
-    <t>Yellow Submarine</t>
-  </si>
-  <si>
-    <t>노란 잠수함</t>
-  </si>
-  <si>
-    <t>Yokai</t>
-  </si>
-  <si>
-    <t>요괴</t>
-  </si>
-  <si>
-    <t>Yooka Laylee</t>
-  </si>
-  <si>
-    <t>유카 레이리</t>
-  </si>
-  <si>
-    <t>Young</t>
-  </si>
-  <si>
-    <t>Youtube</t>
-  </si>
-  <si>
-    <t>유튜브</t>
-  </si>
-  <si>
-    <t>Yu-Gi-Oh</t>
-  </si>
-  <si>
-    <t>Yume Nikki</t>
-  </si>
-  <si>
-    <t>유메 니키</t>
-  </si>
-  <si>
-    <t>Zero no Tsukaima</t>
-  </si>
-  <si>
-    <t>제로 노 쓰카이마</t>
-  </si>
-  <si>
-    <t>Zero Wing</t>
-  </si>
-  <si>
-    <t>제로 윙</t>
-  </si>
-  <si>
-    <t>Zodiac Sign</t>
-  </si>
-  <si>
-    <t>조디악 표지판</t>
-  </si>
-  <si>
-    <t>Zombie</t>
-  </si>
-  <si>
-    <t>좀비</t>
-  </si>
-  <si>
-    <t>Zombie (Vanilla)</t>
-  </si>
-  <si>
-    <t>좀비 (바닐라)</t>
-  </si>
-  <si>
-    <t>Zootopia</t>
-  </si>
-  <si>
-    <t>주토피아</t>
   </si>
   <si>
     <t>Hypixel (Mutations) Tag</t>
@@ -7137,7 +7140,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1177"/>
+  <dimension ref="A1:B1178"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -16549,19 +16552,27 @@
         <v>2254</v>
       </c>
       <c r="B1176" t="s">
-        <v>2255</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B1177" t="s">
         <v>2256</v>
       </c>
-      <c r="B1177" t="s">
+    </row>
+    <row r="1178" spans="1:2">
+      <c r="A1178" t="s">
         <v>2257</v>
       </c>
+      <c r="B1178" t="s">
+        <v>2258</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1177"/>
+  <autoFilter ref="A1:B1178"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ko/headTags.xlsx
+++ b/lang/ko/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1179</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2261">
   <si>
     <t>en</t>
   </si>
@@ -4607,6 +4607,12 @@
   </si>
   <si>
     <t>오픈 소스 개체</t>
+  </si>
+  <si>
+    <t>Opus Magnum</t>
+  </si>
+  <si>
+    <t>오퍼스 매그넘</t>
   </si>
   <si>
     <t>Orb</t>
@@ -7140,7 +7146,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1178"/>
+  <dimension ref="A1:B1179"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13528,12 +13534,12 @@
         <v>1530</v>
       </c>
       <c r="B798" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B799" t="s">
         <v>1532</v>
@@ -13544,12 +13550,12 @@
         <v>1533</v>
       </c>
       <c r="B800" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B801" t="s">
         <v>1535</v>
@@ -13792,36 +13798,36 @@
         <v>1594</v>
       </c>
       <c r="B831" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B832" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B833" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B834" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B835" t="s">
         <v>1599</v>
@@ -13864,12 +13870,12 @@
         <v>1608</v>
       </c>
       <c r="B840" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B841" t="s">
         <v>1610</v>
@@ -14112,12 +14118,12 @@
         <v>1669</v>
       </c>
       <c r="B871" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B872" t="s">
         <v>1671</v>
@@ -14176,20 +14182,20 @@
         <v>1684</v>
       </c>
       <c r="B879" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B880" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B881" t="s">
         <v>1687</v>
@@ -14232,12 +14238,12 @@
         <v>1696</v>
       </c>
       <c r="B886" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B887" t="s">
         <v>1698</v>
@@ -14368,20 +14374,20 @@
         <v>1729</v>
       </c>
       <c r="B903" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B904" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B905" t="s">
         <v>1732</v>
@@ -14392,20 +14398,20 @@
         <v>1733</v>
       </c>
       <c r="B906" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B907" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="B908" t="s">
         <v>1736</v>
@@ -14416,12 +14422,12 @@
         <v>1737</v>
       </c>
       <c r="B909" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B910" t="s">
         <v>1739</v>
@@ -14472,12 +14478,12 @@
         <v>1750</v>
       </c>
       <c r="B916" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B917" t="s">
         <v>1752</v>
@@ -14552,12 +14558,12 @@
         <v>1769</v>
       </c>
       <c r="B926" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="B927" t="s">
         <v>1771</v>
@@ -14992,12 +14998,12 @@
         <v>1878</v>
       </c>
       <c r="B981" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="B982" t="s">
         <v>1880</v>
@@ -15224,12 +15230,12 @@
         <v>1935</v>
       </c>
       <c r="B1010" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="B1011" t="s">
         <v>1937</v>
@@ -15272,12 +15278,12 @@
         <v>1946</v>
       </c>
       <c r="B1016" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="B1017" t="s">
         <v>1948</v>
@@ -15360,12 +15366,12 @@
         <v>1967</v>
       </c>
       <c r="B1027" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="B1028" t="s">
         <v>1969</v>
@@ -15728,12 +15734,12 @@
         <v>2058</v>
       </c>
       <c r="B1073" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="B1074" t="s">
         <v>2060</v>
@@ -15936,12 +15942,12 @@
         <v>2109</v>
       </c>
       <c r="B1099" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="B1100" t="s">
         <v>2111</v>
@@ -16008,12 +16014,12 @@
         <v>2126</v>
       </c>
       <c r="B1108" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="B1109" t="s">
         <v>2128</v>
@@ -16232,12 +16238,12 @@
         <v>2181</v>
       </c>
       <c r="B1136" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="B1137" t="s">
         <v>2183</v>
@@ -16360,12 +16366,12 @@
         <v>2212</v>
       </c>
       <c r="B1152" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="B1153" t="s">
         <v>2214</v>
@@ -16384,12 +16390,12 @@
         <v>2217</v>
       </c>
       <c r="B1155" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="B1156" t="s">
         <v>2219</v>
@@ -16408,12 +16414,12 @@
         <v>2222</v>
       </c>
       <c r="B1158" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="B1159" t="s">
         <v>2224</v>
@@ -16424,12 +16430,12 @@
         <v>2225</v>
       </c>
       <c r="B1160" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="B1161" t="s">
         <v>2227</v>
@@ -16472,12 +16478,12 @@
         <v>2236</v>
       </c>
       <c r="B1166" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="B1167" t="s">
         <v>2238</v>
@@ -16488,12 +16494,12 @@
         <v>2239</v>
       </c>
       <c r="B1168" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="B1169" t="s">
         <v>2241</v>
@@ -16552,15 +16558,15 @@
         <v>2254</v>
       </c>
       <c r="B1176" t="s">
-        <v>2115</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="B1177" t="s">
-        <v>2256</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
@@ -16571,8 +16577,16 @@
         <v>2258</v>
       </c>
     </row>
+    <row r="1179" spans="1:2">
+      <c r="A1179" t="s">
+        <v>2259</v>
+      </c>
+      <c r="B1179" t="s">
+        <v>2260</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1178"/>
+  <autoFilter ref="A1:B1179"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ko/headTags.xlsx
+++ b/lang/ko/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1180</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2263">
   <si>
     <t>en</t>
   </si>
@@ -926,6 +926,12 @@
   </si>
   <si>
     <t>성배</t>
+  </si>
+  <si>
+    <t>Chaos Cubed</t>
+  </si>
+  <si>
+    <t>카오스 큐브</t>
   </si>
   <si>
     <t>Charlie and the Chocolate Factory</t>
@@ -7146,7 +7152,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1179"/>
+  <dimension ref="A1:B1180"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -8502,12 +8508,12 @@
         <v>315</v>
       </c>
       <c r="B169" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B170" t="s">
         <v>317</v>
@@ -8766,12 +8772,12 @@
         <v>380</v>
       </c>
       <c r="B202" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B203" t="s">
         <v>382</v>
@@ -8990,12 +8996,12 @@
         <v>435</v>
       </c>
       <c r="B230" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B231" t="s">
         <v>437</v>
@@ -9086,12 +9092,12 @@
         <v>458</v>
       </c>
       <c r="B242" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="243" spans="1:2">
       <c r="A243" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B243" t="s">
         <v>460</v>
@@ -9270,12 +9276,12 @@
         <v>503</v>
       </c>
       <c r="B265" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B266" t="s">
         <v>505</v>
@@ -9318,12 +9324,12 @@
         <v>514</v>
       </c>
       <c r="B271" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B272" t="s">
         <v>516</v>
@@ -9382,12 +9388,12 @@
         <v>529</v>
       </c>
       <c r="B279" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B280" t="s">
         <v>531</v>
@@ -9462,12 +9468,12 @@
         <v>548</v>
       </c>
       <c r="B289" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B290" t="s">
         <v>550</v>
@@ -9510,20 +9516,20 @@
         <v>559</v>
       </c>
       <c r="B295" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B296" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B297" t="s">
         <v>562</v>
@@ -9622,12 +9628,12 @@
         <v>585</v>
       </c>
       <c r="B309" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B310" t="s">
         <v>587</v>
@@ -9694,28 +9700,28 @@
         <v>602</v>
       </c>
       <c r="B318" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B319" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B320" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B321" t="s">
         <v>606</v>
@@ -9742,12 +9748,12 @@
         <v>611</v>
       </c>
       <c r="B324" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B325" t="s">
         <v>613</v>
@@ -10590,12 +10596,12 @@
         <v>822</v>
       </c>
       <c r="B430" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="431" spans="1:2">
       <c r="A431" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B431" t="s">
         <v>824</v>
@@ -10614,12 +10620,12 @@
         <v>827</v>
       </c>
       <c r="B433" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B434" t="s">
         <v>829</v>
@@ -10662,12 +10668,12 @@
         <v>838</v>
       </c>
       <c r="B439" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B440" t="s">
         <v>840</v>
@@ -10678,12 +10684,12 @@
         <v>841</v>
       </c>
       <c r="B441" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B442" t="s">
         <v>843</v>
@@ -10774,12 +10780,12 @@
         <v>864</v>
       </c>
       <c r="B453" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B454" t="s">
         <v>866</v>
@@ -10894,15 +10900,15 @@
         <v>893</v>
       </c>
       <c r="B468" t="s">
-        <v>158</v>
+        <v>894</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B469" t="s">
-        <v>895</v>
+        <v>158</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -10998,20 +11004,20 @@
         <v>918</v>
       </c>
       <c r="B481" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B482" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B483" t="s">
         <v>921</v>
@@ -11246,12 +11252,12 @@
         <v>978</v>
       </c>
       <c r="B512" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B513" t="s">
         <v>980</v>
@@ -11414,12 +11420,12 @@
         <v>1019</v>
       </c>
       <c r="B533" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="534" spans="1:2">
       <c r="A534" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B534" t="s">
         <v>1021</v>
@@ -11454,12 +11460,12 @@
         <v>1028</v>
       </c>
       <c r="B538" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B539" t="s">
         <v>1030</v>
@@ -11686,12 +11692,12 @@
         <v>1085</v>
       </c>
       <c r="B567" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B568" t="s">
         <v>1087</v>
@@ -11758,12 +11764,12 @@
         <v>1102</v>
       </c>
       <c r="B576" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B577" t="s">
         <v>1104</v>
@@ -11894,12 +11900,12 @@
         <v>1135</v>
       </c>
       <c r="B593" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B594" t="s">
         <v>1137</v>
@@ -12078,12 +12084,12 @@
         <v>1180</v>
       </c>
       <c r="B616" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B617" t="s">
         <v>1182</v>
@@ -12102,23 +12108,23 @@
         <v>1185</v>
       </c>
       <c r="B619" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B620" t="s">
-        <v>866</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B621" t="s">
-        <v>1188</v>
+        <v>868</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -12262,12 +12268,12 @@
         <v>1223</v>
       </c>
       <c r="B639" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B640" t="s">
         <v>1225</v>
@@ -12358,12 +12364,12 @@
         <v>1246</v>
       </c>
       <c r="B651" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B652" t="s">
         <v>1248</v>
@@ -12550,12 +12556,12 @@
         <v>1293</v>
       </c>
       <c r="B675" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B676" t="s">
         <v>1295</v>
@@ -12614,12 +12620,12 @@
         <v>1308</v>
       </c>
       <c r="B683" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B684" t="s">
         <v>1310</v>
@@ -12750,12 +12756,12 @@
         <v>1341</v>
       </c>
       <c r="B700" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B701" t="s">
         <v>1343</v>
@@ -12838,12 +12844,12 @@
         <v>1362</v>
       </c>
       <c r="B711" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B712" t="s">
         <v>1364</v>
@@ -12998,12 +13004,12 @@
         <v>1401</v>
       </c>
       <c r="B731" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B732" t="s">
         <v>1403</v>
@@ -13454,20 +13460,20 @@
         <v>1514</v>
       </c>
       <c r="B788" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B789" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B790" t="s">
         <v>1517</v>
@@ -13478,12 +13484,12 @@
         <v>1518</v>
       </c>
       <c r="B791" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B792" t="s">
         <v>1520</v>
@@ -13510,12 +13516,12 @@
         <v>1525</v>
       </c>
       <c r="B795" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B796" t="s">
         <v>1527</v>
@@ -13542,12 +13548,12 @@
         <v>1532</v>
       </c>
       <c r="B799" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B800" t="s">
         <v>1534</v>
@@ -13558,12 +13564,12 @@
         <v>1535</v>
       </c>
       <c r="B801" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B802" t="s">
         <v>1537</v>
@@ -13806,36 +13812,36 @@
         <v>1596</v>
       </c>
       <c r="B832" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B833" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B834" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B835" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B836" t="s">
         <v>1601</v>
@@ -13878,12 +13884,12 @@
         <v>1610</v>
       </c>
       <c r="B841" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B842" t="s">
         <v>1612</v>
@@ -14126,12 +14132,12 @@
         <v>1671</v>
       </c>
       <c r="B872" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B873" t="s">
         <v>1673</v>
@@ -14190,20 +14196,20 @@
         <v>1686</v>
       </c>
       <c r="B880" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B881" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B882" t="s">
         <v>1689</v>
@@ -14246,12 +14252,12 @@
         <v>1698</v>
       </c>
       <c r="B887" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B888" t="s">
         <v>1700</v>
@@ -14382,20 +14388,20 @@
         <v>1731</v>
       </c>
       <c r="B904" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B905" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B906" t="s">
         <v>1734</v>
@@ -14406,20 +14412,20 @@
         <v>1735</v>
       </c>
       <c r="B907" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B908" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="B909" t="s">
         <v>1738</v>
@@ -14430,12 +14436,12 @@
         <v>1739</v>
       </c>
       <c r="B910" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="B911" t="s">
         <v>1741</v>
@@ -14486,12 +14492,12 @@
         <v>1752</v>
       </c>
       <c r="B917" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B918" t="s">
         <v>1754</v>
@@ -14566,12 +14572,12 @@
         <v>1771</v>
       </c>
       <c r="B927" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="B928" t="s">
         <v>1773</v>
@@ -15006,12 +15012,12 @@
         <v>1880</v>
       </c>
       <c r="B982" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B983" t="s">
         <v>1882</v>
@@ -15238,12 +15244,12 @@
         <v>1937</v>
       </c>
       <c r="B1011" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="B1012" t="s">
         <v>1939</v>
@@ -15286,12 +15292,12 @@
         <v>1948</v>
       </c>
       <c r="B1017" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="B1018" t="s">
         <v>1950</v>
@@ -15374,12 +15380,12 @@
         <v>1969</v>
       </c>
       <c r="B1028" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="B1029" t="s">
         <v>1971</v>
@@ -15742,12 +15748,12 @@
         <v>2060</v>
       </c>
       <c r="B1074" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="B1075" t="s">
         <v>2062</v>
@@ -15950,12 +15956,12 @@
         <v>2111</v>
       </c>
       <c r="B1100" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="B1101" t="s">
         <v>2113</v>
@@ -16022,12 +16028,12 @@
         <v>2128</v>
       </c>
       <c r="B1109" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="B1110" t="s">
         <v>2130</v>
@@ -16246,12 +16252,12 @@
         <v>2183</v>
       </c>
       <c r="B1137" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="B1138" t="s">
         <v>2185</v>
@@ -16374,12 +16380,12 @@
         <v>2214</v>
       </c>
       <c r="B1153" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="B1154" t="s">
         <v>2216</v>
@@ -16398,12 +16404,12 @@
         <v>2219</v>
       </c>
       <c r="B1156" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="B1157" t="s">
         <v>2221</v>
@@ -16422,12 +16428,12 @@
         <v>2224</v>
       </c>
       <c r="B1159" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="B1160" t="s">
         <v>2226</v>
@@ -16438,12 +16444,12 @@
         <v>2227</v>
       </c>
       <c r="B1161" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="B1162" t="s">
         <v>2229</v>
@@ -16486,12 +16492,12 @@
         <v>2238</v>
       </c>
       <c r="B1167" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="B1168" t="s">
         <v>2240</v>
@@ -16502,12 +16508,12 @@
         <v>2241</v>
       </c>
       <c r="B1169" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="B1170" t="s">
         <v>2243</v>
@@ -16566,15 +16572,15 @@
         <v>2256</v>
       </c>
       <c r="B1177" t="s">
-        <v>2117</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="B1178" t="s">
-        <v>2258</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
@@ -16585,8 +16591,16 @@
         <v>2260</v>
       </c>
     </row>
+    <row r="1180" spans="1:2">
+      <c r="A1180" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>2262</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1179"/>
+  <autoFilter ref="A1:B1180"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ko/headTags.xlsx
+++ b/lang/ko/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1181</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2265">
   <si>
     <t>en</t>
   </si>
@@ -4982,6 +4982,12 @@
   </si>
   <si>
     <t>팝 팀 에픽</t>
+  </si>
+  <si>
+    <t>Popee the Performer</t>
+  </si>
+  <si>
+    <t>공연자 포피</t>
   </si>
   <si>
     <t>POPGOES</t>
@@ -7152,7 +7158,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1180"/>
+  <dimension ref="A1:B1181"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14140,12 +14146,12 @@
         <v>1673</v>
       </c>
       <c r="B873" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B874" t="s">
         <v>1675</v>
@@ -14204,20 +14210,20 @@
         <v>1688</v>
       </c>
       <c r="B881" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B882" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B883" t="s">
         <v>1691</v>
@@ -14260,12 +14266,12 @@
         <v>1700</v>
       </c>
       <c r="B888" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B889" t="s">
         <v>1702</v>
@@ -14396,20 +14402,20 @@
         <v>1733</v>
       </c>
       <c r="B905" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B906" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="B907" t="s">
         <v>1736</v>
@@ -14420,20 +14426,20 @@
         <v>1737</v>
       </c>
       <c r="B908" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B909" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B910" t="s">
         <v>1740</v>
@@ -14444,12 +14450,12 @@
         <v>1741</v>
       </c>
       <c r="B911" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B912" t="s">
         <v>1743</v>
@@ -14500,12 +14506,12 @@
         <v>1754</v>
       </c>
       <c r="B918" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B919" t="s">
         <v>1756</v>
@@ -14580,12 +14586,12 @@
         <v>1773</v>
       </c>
       <c r="B928" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B929" t="s">
         <v>1775</v>
@@ -15020,12 +15026,12 @@
         <v>1882</v>
       </c>
       <c r="B983" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="B984" t="s">
         <v>1884</v>
@@ -15252,12 +15258,12 @@
         <v>1939</v>
       </c>
       <c r="B1012" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="B1013" t="s">
         <v>1941</v>
@@ -15300,12 +15306,12 @@
         <v>1950</v>
       </c>
       <c r="B1018" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="B1019" t="s">
         <v>1952</v>
@@ -15388,12 +15394,12 @@
         <v>1971</v>
       </c>
       <c r="B1029" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="B1030" t="s">
         <v>1973</v>
@@ -15756,12 +15762,12 @@
         <v>2062</v>
       </c>
       <c r="B1075" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="B1076" t="s">
         <v>2064</v>
@@ -15964,12 +15970,12 @@
         <v>2113</v>
       </c>
       <c r="B1101" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="B1102" t="s">
         <v>2115</v>
@@ -16036,12 +16042,12 @@
         <v>2130</v>
       </c>
       <c r="B1110" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="B1111" t="s">
         <v>2132</v>
@@ -16260,12 +16266,12 @@
         <v>2185</v>
       </c>
       <c r="B1138" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="B1139" t="s">
         <v>2187</v>
@@ -16388,12 +16394,12 @@
         <v>2216</v>
       </c>
       <c r="B1154" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="B1155" t="s">
         <v>2218</v>
@@ -16412,12 +16418,12 @@
         <v>2221</v>
       </c>
       <c r="B1157" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="B1158" t="s">
         <v>2223</v>
@@ -16436,12 +16442,12 @@
         <v>2226</v>
       </c>
       <c r="B1160" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="B1161" t="s">
         <v>2228</v>
@@ -16452,12 +16458,12 @@
         <v>2229</v>
       </c>
       <c r="B1162" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="B1163" t="s">
         <v>2231</v>
@@ -16500,12 +16506,12 @@
         <v>2240</v>
       </c>
       <c r="B1168" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="B1169" t="s">
         <v>2242</v>
@@ -16516,12 +16522,12 @@
         <v>2243</v>
       </c>
       <c r="B1170" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="B1171" t="s">
         <v>2245</v>
@@ -16580,15 +16586,15 @@
         <v>2258</v>
       </c>
       <c r="B1178" t="s">
-        <v>2119</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="B1179" t="s">
-        <v>2260</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
@@ -16599,8 +16605,16 @@
         <v>2262</v>
       </c>
     </row>
+    <row r="1181" spans="1:2">
+      <c r="A1181" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>2264</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1180"/>
+  <autoFilter ref="A1:B1181"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ko/headTags.xlsx
+++ b/lang/ko/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1182</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2267">
   <si>
     <t>en</t>
   </si>
@@ -6224,6 +6224,12 @@
   </si>
   <si>
     <t>팅커의 건설</t>
+  </si>
+  <si>
+    <t>Tiny Takeover</t>
+  </si>
+  <si>
+    <t>작은 인수</t>
   </si>
   <si>
     <t>Titanfall</t>
@@ -7158,7 +7164,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1181"/>
+  <dimension ref="A1:B1182"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -15978,12 +15984,12 @@
         <v>2115</v>
       </c>
       <c r="B1102" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="B1103" t="s">
         <v>2117</v>
@@ -16050,12 +16056,12 @@
         <v>2132</v>
       </c>
       <c r="B1111" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="B1112" t="s">
         <v>2134</v>
@@ -16274,12 +16280,12 @@
         <v>2187</v>
       </c>
       <c r="B1139" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="B1140" t="s">
         <v>2189</v>
@@ -16402,12 +16408,12 @@
         <v>2218</v>
       </c>
       <c r="B1155" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="B1156" t="s">
         <v>2220</v>
@@ -16426,12 +16432,12 @@
         <v>2223</v>
       </c>
       <c r="B1158" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="B1159" t="s">
         <v>2225</v>
@@ -16450,12 +16456,12 @@
         <v>2228</v>
       </c>
       <c r="B1161" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="B1162" t="s">
         <v>2230</v>
@@ -16466,12 +16472,12 @@
         <v>2231</v>
       </c>
       <c r="B1163" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="B1164" t="s">
         <v>2233</v>
@@ -16514,12 +16520,12 @@
         <v>2242</v>
       </c>
       <c r="B1169" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="B1170" t="s">
         <v>2244</v>
@@ -16530,12 +16536,12 @@
         <v>2245</v>
       </c>
       <c r="B1171" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="B1172" t="s">
         <v>2247</v>
@@ -16594,15 +16600,15 @@
         <v>2260</v>
       </c>
       <c r="B1179" t="s">
-        <v>2121</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="B1180" t="s">
-        <v>2262</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
@@ -16613,8 +16619,16 @@
         <v>2264</v>
       </c>
     </row>
+    <row r="1182" spans="1:2">
+      <c r="A1182" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>2266</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1181"/>
+  <autoFilter ref="A1:B1182"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ko/headTags.xlsx
+++ b/lang/ko/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1186</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2275">
   <si>
     <t>en</t>
   </si>
@@ -3346,6 +3346,12 @@
     <t>하이픽셀</t>
   </si>
   <si>
+    <t>Hypixel (Abiphone)</t>
+  </si>
+  <si>
+    <t>하이픽셀(아비폰)</t>
+  </si>
+  <si>
     <t>Hypixel (Attribute Shard)</t>
   </si>
   <si>
@@ -3370,6 +3376,12 @@
     <t>하이픽셀(기어)</t>
   </si>
   <si>
+    <t>Hypixel (Gemstone)</t>
+  </si>
+  <si>
+    <t>하이픽셀(보석)</t>
+  </si>
+  <si>
     <t>Hypixel (Minion)</t>
   </si>
   <si>
@@ -3388,6 +3400,12 @@
     <t>하이픽셀(NPC)</t>
   </si>
   <si>
+    <t>Hypixel (Pet Items)</t>
+  </si>
+  <si>
+    <t>하이픽셀(애완동물 아이템)</t>
+  </si>
+  <si>
     <t>Hypixel (Pets)</t>
   </si>
   <si>
@@ -3398,6 +3416,12 @@
   </si>
   <si>
     <t>하이픽셀 (재련석)</t>
+  </si>
+  <si>
+    <t>Hypixel (Runes)</t>
+  </si>
+  <si>
+    <t>하이픽셀(룬)</t>
   </si>
   <si>
     <t>Hypixel (Sacks)</t>
@@ -7164,7 +7188,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1182"/>
+  <dimension ref="A1:B1186"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -11920,36 +11944,36 @@
         <v>1137</v>
       </c>
       <c r="B594" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B595" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B596" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B597" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B598" t="s">
         <v>1145</v>
@@ -12104,71 +12128,71 @@
         <v>1182</v>
       </c>
       <c r="B617" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="618" spans="1:2">
       <c r="A618" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B618" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B619" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B620" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="B621" t="s">
-        <v>868</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="B622" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="B623" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="B624" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B625" t="s">
-        <v>1196</v>
+        <v>868</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -12288,36 +12312,36 @@
         <v>1225</v>
       </c>
       <c r="B640" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B641" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B642" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B643" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B644" t="s">
         <v>1233</v>
@@ -12384,36 +12408,36 @@
         <v>1248</v>
       </c>
       <c r="B652" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B653" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B654" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="655" spans="1:2">
       <c r="A655" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B655" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="656" spans="1:2">
       <c r="A656" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B656" t="s">
         <v>1256</v>
@@ -12576,36 +12600,36 @@
         <v>1295</v>
       </c>
       <c r="B676" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B677" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B678" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B679" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B680" t="s">
         <v>1303</v>
@@ -12640,36 +12664,36 @@
         <v>1310</v>
       </c>
       <c r="B684" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B685" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B686" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B687" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="688" spans="1:2">
       <c r="A688" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B688" t="s">
         <v>1318</v>
@@ -12776,36 +12800,36 @@
         <v>1343</v>
       </c>
       <c r="B701" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B702" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B703" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B704" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B705" t="s">
         <v>1351</v>
@@ -12864,36 +12888,36 @@
         <v>1364</v>
       </c>
       <c r="B712" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B713" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B714" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B715" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B716" t="s">
         <v>1372</v>
@@ -13024,36 +13048,36 @@
         <v>1403</v>
       </c>
       <c r="B732" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B733" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B734" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B735" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B736" t="s">
         <v>1411</v>
@@ -13480,140 +13504,140 @@
         <v>1516</v>
       </c>
       <c r="B789" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B790" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="B791" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="B792" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1521</v>
+        <v>1524</v>
       </c>
       <c r="B793" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="B794" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B795" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B796" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B797" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B798" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B799" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B800" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B801" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B802" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="B803" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="B804" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B805" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B806" t="s">
         <v>1545</v>
@@ -13832,60 +13856,60 @@
         <v>1598</v>
       </c>
       <c r="B833" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B834" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="B835" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="B836" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="B837" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1604</v>
+        <v>1607</v>
       </c>
       <c r="B838" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="B839" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B840" t="s">
         <v>1609</v>
@@ -13904,36 +13928,36 @@
         <v>1612</v>
       </c>
       <c r="B842" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B843" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B844" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B845" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B846" t="s">
         <v>1620</v>
@@ -14160,36 +14184,36 @@
         <v>1675</v>
       </c>
       <c r="B874" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B875" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B876" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B877" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B878" t="s">
         <v>1683</v>
@@ -14224,44 +14248,44 @@
         <v>1690</v>
       </c>
       <c r="B882" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B883" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="B884" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="B885" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="B886" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B887" t="s">
         <v>1699</v>
@@ -14280,36 +14304,36 @@
         <v>1702</v>
       </c>
       <c r="B889" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B890" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B891" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B892" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B893" t="s">
         <v>1710</v>
@@ -14416,84 +14440,84 @@
         <v>1735</v>
       </c>
       <c r="B906" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B907" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="B908" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="B909" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
       <c r="B910" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
       <c r="B911" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="B912" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="B913" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="B914" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="B915" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B916" t="s">
         <v>1751</v>
@@ -14520,36 +14544,36 @@
         <v>1756</v>
       </c>
       <c r="B919" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="B920" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B921" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="B922" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B923" t="s">
         <v>1764</v>
@@ -14600,36 +14624,36 @@
         <v>1775</v>
       </c>
       <c r="B929" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B930" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="B931" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="932" spans="1:2">
       <c r="A932" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B932" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="B933" t="s">
         <v>1783</v>
@@ -15040,36 +15064,36 @@
         <v>1884</v>
       </c>
       <c r="B984" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="B985" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="B986" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="B987" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B988" t="s">
         <v>1892</v>
@@ -15272,36 +15296,36 @@
         <v>1941</v>
       </c>
       <c r="B1013" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="B1014" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="B1015" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="B1016" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="B1017" t="s">
         <v>1949</v>
@@ -15320,36 +15344,36 @@
         <v>1952</v>
       </c>
       <c r="B1019" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="B1020" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="B1021" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="B1022" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="B1023" t="s">
         <v>1960</v>
@@ -15408,36 +15432,36 @@
         <v>1973</v>
       </c>
       <c r="B1030" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B1031" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B1032" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="B1033" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="B1034" t="s">
         <v>1981</v>
@@ -15776,36 +15800,36 @@
         <v>2064</v>
       </c>
       <c r="B1076" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="B1077" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="B1078" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="B1079" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="B1080" t="s">
         <v>2072</v>
@@ -15992,36 +16016,36 @@
         <v>2117</v>
       </c>
       <c r="B1103" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="B1104" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="B1105" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="B1106" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="B1107" t="s">
         <v>2125</v>
@@ -16064,36 +16088,36 @@
         <v>2134</v>
       </c>
       <c r="B1112" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="B1113" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="B1114" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="B1115" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="B1116" t="s">
         <v>2142</v>
@@ -16288,36 +16312,36 @@
         <v>2189</v>
       </c>
       <c r="B1140" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="B1141" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="B1142" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="B1143" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="B1144" t="s">
         <v>2197</v>
@@ -16416,100 +16440,100 @@
         <v>2220</v>
       </c>
       <c r="B1156" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="B1157" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="B1158" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="B1159" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
       <c r="B1160" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="B1161" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="B1162" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
       <c r="B1163" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="B1164" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="B1165" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="B1166" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="B1167" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="B1168" t="s">
         <v>2241</v>
@@ -16528,52 +16552,52 @@
         <v>2244</v>
       </c>
       <c r="B1170" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="B1171" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="B1172" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="B1173" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="B1174" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="B1175" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="B1176" t="s">
         <v>2255</v>
@@ -16608,27 +16632,59 @@
         <v>2262</v>
       </c>
       <c r="B1180" t="s">
-        <v>2123</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="B1181" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="B1182" t="s">
-        <v>2266</v>
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:2">
+      <c r="A1183" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:2">
+      <c r="A1184" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:2">
+      <c r="A1185" t="s">
+        <v>2271</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:2">
+      <c r="A1186" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>2274</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1182"/>
+  <autoFilter ref="A1:B1186"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ko/headTags.xlsx
+++ b/lang/ko/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1187</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2277">
   <si>
     <t>en</t>
   </si>
@@ -5087,6 +5087,12 @@
   </si>
   <si>
     <t>레이튼 교수</t>
+  </si>
+  <si>
+    <t>Project Zomboid</t>
+  </si>
+  <si>
+    <t>프로젝트 좀보이드</t>
   </si>
   <si>
     <t>Pumpkin</t>
@@ -7188,7 +7194,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1186"/>
+  <dimension ref="A1:B1187"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14280,20 +14286,20 @@
         <v>1698</v>
       </c>
       <c r="B886" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B887" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B888" t="s">
         <v>1701</v>
@@ -14336,12 +14342,12 @@
         <v>1710</v>
       </c>
       <c r="B893" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B894" t="s">
         <v>1712</v>
@@ -14472,20 +14478,20 @@
         <v>1743</v>
       </c>
       <c r="B910" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B911" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B912" t="s">
         <v>1746</v>
@@ -14496,20 +14502,20 @@
         <v>1747</v>
       </c>
       <c r="B913" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="B914" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B915" t="s">
         <v>1750</v>
@@ -14520,12 +14526,12 @@
         <v>1751</v>
       </c>
       <c r="B916" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B917" t="s">
         <v>1753</v>
@@ -14576,12 +14582,12 @@
         <v>1764</v>
       </c>
       <c r="B923" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="B924" t="s">
         <v>1766</v>
@@ -14656,12 +14662,12 @@
         <v>1783</v>
       </c>
       <c r="B933" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="B934" t="s">
         <v>1785</v>
@@ -15096,12 +15102,12 @@
         <v>1892</v>
       </c>
       <c r="B988" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="B989" t="s">
         <v>1894</v>
@@ -15328,12 +15334,12 @@
         <v>1949</v>
       </c>
       <c r="B1017" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="B1018" t="s">
         <v>1951</v>
@@ -15376,12 +15382,12 @@
         <v>1960</v>
       </c>
       <c r="B1023" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="B1024" t="s">
         <v>1962</v>
@@ -15464,12 +15470,12 @@
         <v>1981</v>
       </c>
       <c r="B1034" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B1035" t="s">
         <v>1983</v>
@@ -15832,12 +15838,12 @@
         <v>2072</v>
       </c>
       <c r="B1080" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="B1081" t="s">
         <v>2074</v>
@@ -16048,12 +16054,12 @@
         <v>2125</v>
       </c>
       <c r="B1107" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="B1108" t="s">
         <v>2127</v>
@@ -16120,12 +16126,12 @@
         <v>2142</v>
       </c>
       <c r="B1116" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="B1117" t="s">
         <v>2144</v>
@@ -16344,12 +16350,12 @@
         <v>2197</v>
       </c>
       <c r="B1144" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="B1145" t="s">
         <v>2199</v>
@@ -16472,12 +16478,12 @@
         <v>2228</v>
       </c>
       <c r="B1160" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="B1161" t="s">
         <v>2230</v>
@@ -16496,12 +16502,12 @@
         <v>2233</v>
       </c>
       <c r="B1163" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="B1164" t="s">
         <v>2235</v>
@@ -16520,12 +16526,12 @@
         <v>2238</v>
       </c>
       <c r="B1166" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="B1167" t="s">
         <v>2240</v>
@@ -16536,12 +16542,12 @@
         <v>2241</v>
       </c>
       <c r="B1168" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="B1169" t="s">
         <v>2243</v>
@@ -16584,12 +16590,12 @@
         <v>2252</v>
       </c>
       <c r="B1174" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="B1175" t="s">
         <v>2254</v>
@@ -16600,12 +16606,12 @@
         <v>2255</v>
       </c>
       <c r="B1176" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="B1177" t="s">
         <v>2257</v>
@@ -16664,15 +16670,15 @@
         <v>2270</v>
       </c>
       <c r="B1184" t="s">
-        <v>2131</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="B1185" t="s">
-        <v>2272</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
@@ -16683,8 +16689,16 @@
         <v>2274</v>
       </c>
     </row>
+    <row r="1187" spans="1:2">
+      <c r="A1187" t="s">
+        <v>2275</v>
+      </c>
+      <c r="B1187" t="s">
+        <v>2276</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1186"/>
+  <autoFilter ref="A1:B1187"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ko/headTags.xlsx
+++ b/lang/ko/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1188</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2279">
   <si>
     <t>en</t>
   </si>
@@ -410,6 +410,12 @@
   </si>
   <si>
     <t>바카 및 테스트</t>
+  </si>
+  <si>
+    <t>Bakugan</t>
+  </si>
+  <si>
+    <t>바쿠간</t>
   </si>
   <si>
     <t>Baldi's Basics</t>
@@ -7194,7 +7200,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1187"/>
+  <dimension ref="A1:B1188"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -7766,28 +7772,28 @@
         <v>135</v>
       </c>
       <c r="B71" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B72" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B73" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B74" t="s">
         <v>139</v>
@@ -7862,12 +7868,12 @@
         <v>156</v>
       </c>
       <c r="B83" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B84" t="s">
         <v>158</v>
@@ -7926,12 +7932,12 @@
         <v>171</v>
       </c>
       <c r="B91" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B92" t="s">
         <v>173</v>
@@ -7990,12 +7996,12 @@
         <v>186</v>
       </c>
       <c r="B99" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B100" t="s">
         <v>188</v>
@@ -8038,12 +8044,12 @@
         <v>197</v>
       </c>
       <c r="B105" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B106" t="s">
         <v>199</v>
@@ -8054,12 +8060,12 @@
         <v>200</v>
       </c>
       <c r="B107" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B108" t="s">
         <v>202</v>
@@ -8086,20 +8092,20 @@
         <v>207</v>
       </c>
       <c r="B111" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B112" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B113" t="s">
         <v>210</v>
@@ -8118,12 +8124,12 @@
         <v>213</v>
       </c>
       <c r="B115" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B116" t="s">
         <v>215</v>
@@ -8230,20 +8236,20 @@
         <v>240</v>
       </c>
       <c r="B129" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B130" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B131" t="s">
         <v>243</v>
@@ -8294,12 +8300,12 @@
         <v>254</v>
       </c>
       <c r="B137" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B138" t="s">
         <v>256</v>
@@ -8310,12 +8316,12 @@
         <v>257</v>
       </c>
       <c r="B139" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B140" t="s">
         <v>259</v>
@@ -8334,12 +8340,12 @@
         <v>262</v>
       </c>
       <c r="B142" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B143" t="s">
         <v>264</v>
@@ -8558,12 +8564,12 @@
         <v>317</v>
       </c>
       <c r="B170" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B171" t="s">
         <v>319</v>
@@ -8822,12 +8828,12 @@
         <v>382</v>
       </c>
       <c r="B203" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B204" t="s">
         <v>384</v>
@@ -9046,12 +9052,12 @@
         <v>437</v>
       </c>
       <c r="B231" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B232" t="s">
         <v>439</v>
@@ -9142,12 +9148,12 @@
         <v>460</v>
       </c>
       <c r="B243" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B244" t="s">
         <v>462</v>
@@ -9326,12 +9332,12 @@
         <v>505</v>
       </c>
       <c r="B266" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B267" t="s">
         <v>507</v>
@@ -9374,12 +9380,12 @@
         <v>516</v>
       </c>
       <c r="B272" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B273" t="s">
         <v>518</v>
@@ -9438,12 +9444,12 @@
         <v>531</v>
       </c>
       <c r="B280" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B281" t="s">
         <v>533</v>
@@ -9518,12 +9524,12 @@
         <v>550</v>
       </c>
       <c r="B290" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="291" spans="1:2">
       <c r="A291" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B291" t="s">
         <v>552</v>
@@ -9566,20 +9572,20 @@
         <v>561</v>
       </c>
       <c r="B296" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B297" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B298" t="s">
         <v>564</v>
@@ -9678,12 +9684,12 @@
         <v>587</v>
       </c>
       <c r="B310" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="311" spans="1:2">
       <c r="A311" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B311" t="s">
         <v>589</v>
@@ -9750,28 +9756,28 @@
         <v>604</v>
       </c>
       <c r="B319" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B320" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B321" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B322" t="s">
         <v>608</v>
@@ -9798,12 +9804,12 @@
         <v>613</v>
       </c>
       <c r="B325" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B326" t="s">
         <v>615</v>
@@ -10646,12 +10652,12 @@
         <v>824</v>
       </c>
       <c r="B431" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B432" t="s">
         <v>826</v>
@@ -10670,12 +10676,12 @@
         <v>829</v>
       </c>
       <c r="B434" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B435" t="s">
         <v>831</v>
@@ -10718,12 +10724,12 @@
         <v>840</v>
       </c>
       <c r="B440" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="441" spans="1:2">
       <c r="A441" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B441" t="s">
         <v>842</v>
@@ -10734,12 +10740,12 @@
         <v>843</v>
       </c>
       <c r="B442" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="443" spans="1:2">
       <c r="A443" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B443" t="s">
         <v>845</v>
@@ -10830,12 +10836,12 @@
         <v>866</v>
       </c>
       <c r="B454" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="455" spans="1:2">
       <c r="A455" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B455" t="s">
         <v>868</v>
@@ -10950,15 +10956,15 @@
         <v>895</v>
       </c>
       <c r="B469" t="s">
-        <v>158</v>
+        <v>896</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B470" t="s">
-        <v>897</v>
+        <v>160</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -11054,20 +11060,20 @@
         <v>920</v>
       </c>
       <c r="B482" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B483" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B484" t="s">
         <v>923</v>
@@ -11302,12 +11308,12 @@
         <v>980</v>
       </c>
       <c r="B513" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="A514" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B514" t="s">
         <v>982</v>
@@ -11470,12 +11476,12 @@
         <v>1021</v>
       </c>
       <c r="B534" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B535" t="s">
         <v>1023</v>
@@ -11510,12 +11516,12 @@
         <v>1030</v>
       </c>
       <c r="B539" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B540" t="s">
         <v>1032</v>
@@ -11742,12 +11748,12 @@
         <v>1087</v>
       </c>
       <c r="B568" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B569" t="s">
         <v>1089</v>
@@ -11814,12 +11820,12 @@
         <v>1104</v>
       </c>
       <c r="B577" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B578" t="s">
         <v>1106</v>
@@ -11982,12 +11988,12 @@
         <v>1145</v>
       </c>
       <c r="B598" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B599" t="s">
         <v>1147</v>
@@ -12166,12 +12172,12 @@
         <v>1190</v>
       </c>
       <c r="B621" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B622" t="s">
         <v>1192</v>
@@ -12190,23 +12196,23 @@
         <v>1195</v>
       </c>
       <c r="B624" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B625" t="s">
-        <v>868</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B626" t="s">
-        <v>1198</v>
+        <v>870</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -12350,12 +12356,12 @@
         <v>1233</v>
       </c>
       <c r="B644" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B645" t="s">
         <v>1235</v>
@@ -12446,12 +12452,12 @@
         <v>1256</v>
       </c>
       <c r="B656" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B657" t="s">
         <v>1258</v>
@@ -12638,12 +12644,12 @@
         <v>1303</v>
       </c>
       <c r="B680" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B681" t="s">
         <v>1305</v>
@@ -12702,12 +12708,12 @@
         <v>1318</v>
       </c>
       <c r="B688" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="689" spans="1:2">
       <c r="A689" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B689" t="s">
         <v>1320</v>
@@ -12838,12 +12844,12 @@
         <v>1351</v>
       </c>
       <c r="B705" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B706" t="s">
         <v>1353</v>
@@ -12926,12 +12932,12 @@
         <v>1372</v>
       </c>
       <c r="B716" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B717" t="s">
         <v>1374</v>
@@ -13086,12 +13092,12 @@
         <v>1411</v>
       </c>
       <c r="B736" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B737" t="s">
         <v>1413</v>
@@ -13542,20 +13548,20 @@
         <v>1524</v>
       </c>
       <c r="B793" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B794" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B795" t="s">
         <v>1527</v>
@@ -13566,12 +13572,12 @@
         <v>1528</v>
       </c>
       <c r="B796" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B797" t="s">
         <v>1530</v>
@@ -13598,12 +13604,12 @@
         <v>1535</v>
       </c>
       <c r="B800" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B801" t="s">
         <v>1537</v>
@@ -13630,12 +13636,12 @@
         <v>1542</v>
       </c>
       <c r="B804" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B805" t="s">
         <v>1544</v>
@@ -13646,12 +13652,12 @@
         <v>1545</v>
       </c>
       <c r="B806" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B807" t="s">
         <v>1547</v>
@@ -13894,36 +13900,36 @@
         <v>1606</v>
       </c>
       <c r="B837" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B838" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B839" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B840" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B841" t="s">
         <v>1611</v>
@@ -13966,12 +13972,12 @@
         <v>1620</v>
       </c>
       <c r="B846" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B847" t="s">
         <v>1622</v>
@@ -14222,12 +14228,12 @@
         <v>1683</v>
       </c>
       <c r="B878" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B879" t="s">
         <v>1685</v>
@@ -14294,20 +14300,20 @@
         <v>1700</v>
       </c>
       <c r="B887" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B888" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B889" t="s">
         <v>1703</v>
@@ -14350,12 +14356,12 @@
         <v>1712</v>
       </c>
       <c r="B894" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="B895" t="s">
         <v>1714</v>
@@ -14486,20 +14492,20 @@
         <v>1745</v>
       </c>
       <c r="B911" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B912" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B913" t="s">
         <v>1748</v>
@@ -14510,20 +14516,20 @@
         <v>1749</v>
       </c>
       <c r="B914" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B915" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B916" t="s">
         <v>1752</v>
@@ -14534,12 +14540,12 @@
         <v>1753</v>
       </c>
       <c r="B917" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B918" t="s">
         <v>1755</v>
@@ -14590,12 +14596,12 @@
         <v>1766</v>
       </c>
       <c r="B924" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="B925" t="s">
         <v>1768</v>
@@ -14670,12 +14676,12 @@
         <v>1785</v>
       </c>
       <c r="B934" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B935" t="s">
         <v>1787</v>
@@ -15110,12 +15116,12 @@
         <v>1894</v>
       </c>
       <c r="B989" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B990" t="s">
         <v>1896</v>
@@ -15342,12 +15348,12 @@
         <v>1951</v>
       </c>
       <c r="B1018" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="B1019" t="s">
         <v>1953</v>
@@ -15390,12 +15396,12 @@
         <v>1962</v>
       </c>
       <c r="B1024" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="B1025" t="s">
         <v>1964</v>
@@ -15478,12 +15484,12 @@
         <v>1983</v>
       </c>
       <c r="B1035" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="B1036" t="s">
         <v>1985</v>
@@ -15846,12 +15852,12 @@
         <v>2074</v>
       </c>
       <c r="B1081" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="B1082" t="s">
         <v>2076</v>
@@ -16062,12 +16068,12 @@
         <v>2127</v>
       </c>
       <c r="B1108" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="B1109" t="s">
         <v>2129</v>
@@ -16134,12 +16140,12 @@
         <v>2144</v>
       </c>
       <c r="B1117" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="B1118" t="s">
         <v>2146</v>
@@ -16358,12 +16364,12 @@
         <v>2199</v>
       </c>
       <c r="B1145" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="B1146" t="s">
         <v>2201</v>
@@ -16486,12 +16492,12 @@
         <v>2230</v>
       </c>
       <c r="B1161" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="B1162" t="s">
         <v>2232</v>
@@ -16510,12 +16516,12 @@
         <v>2235</v>
       </c>
       <c r="B1164" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="B1165" t="s">
         <v>2237</v>
@@ -16534,12 +16540,12 @@
         <v>2240</v>
       </c>
       <c r="B1167" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="B1168" t="s">
         <v>2242</v>
@@ -16550,12 +16556,12 @@
         <v>2243</v>
       </c>
       <c r="B1169" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="B1170" t="s">
         <v>2245</v>
@@ -16598,12 +16604,12 @@
         <v>2254</v>
       </c>
       <c r="B1175" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="B1176" t="s">
         <v>2256</v>
@@ -16614,12 +16620,12 @@
         <v>2257</v>
       </c>
       <c r="B1177" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="B1178" t="s">
         <v>2259</v>
@@ -16678,15 +16684,15 @@
         <v>2272</v>
       </c>
       <c r="B1185" t="s">
-        <v>2133</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="B1186" t="s">
-        <v>2274</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
@@ -16697,8 +16703,16 @@
         <v>2276</v>
       </c>
     </row>
+    <row r="1188" spans="1:2">
+      <c r="A1188" t="s">
+        <v>2277</v>
+      </c>
+      <c r="B1188" t="s">
+        <v>2278</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1187"/>
+  <autoFilter ref="A1:B1188"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ko/headTags.xlsx
+++ b/lang/ko/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2280">
   <si>
     <t>en</t>
   </si>
@@ -5459,6 +5459,9 @@
   </si>
   <si>
     <t>모르도르의 그림자</t>
+  </si>
+  <si>
+    <t>Shark</t>
   </si>
   <si>
     <t>Sheep</t>
@@ -7200,7 +7203,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1188"/>
+  <dimension ref="A1:B1189"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14796,332 +14799,332 @@
         <v>1814</v>
       </c>
       <c r="B949" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B950" t="s">
         <v>1816</v>
-      </c>
-      <c r="B950" t="s">
-        <v>1817</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B951" t="s">
         <v>1818</v>
-      </c>
-      <c r="B951" t="s">
-        <v>1819</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B952" t="s">
         <v>1820</v>
-      </c>
-      <c r="B952" t="s">
-        <v>1821</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B953" t="s">
         <v>1822</v>
-      </c>
-      <c r="B953" t="s">
-        <v>1823</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B954" t="s">
         <v>1824</v>
-      </c>
-      <c r="B954" t="s">
-        <v>1825</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B955" t="s">
         <v>1826</v>
-      </c>
-      <c r="B955" t="s">
-        <v>1827</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B956" t="s">
         <v>1828</v>
-      </c>
-      <c r="B956" t="s">
-        <v>1829</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B957" t="s">
         <v>1830</v>
-      </c>
-      <c r="B957" t="s">
-        <v>1831</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B958" t="s">
         <v>1832</v>
-      </c>
-      <c r="B958" t="s">
-        <v>1833</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B959" t="s">
         <v>1834</v>
-      </c>
-      <c r="B959" t="s">
-        <v>1835</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B960" t="s">
         <v>1836</v>
-      </c>
-      <c r="B960" t="s">
-        <v>1837</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B961" t="s">
         <v>1838</v>
-      </c>
-      <c r="B961" t="s">
-        <v>1839</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B962" t="s">
         <v>1840</v>
-      </c>
-      <c r="B962" t="s">
-        <v>1841</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B963" t="s">
         <v>1842</v>
-      </c>
-      <c r="B963" t="s">
-        <v>1843</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B964" t="s">
         <v>1844</v>
-      </c>
-      <c r="B964" t="s">
-        <v>1845</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B965" t="s">
         <v>1846</v>
-      </c>
-      <c r="B965" t="s">
-        <v>1847</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B966" t="s">
         <v>1848</v>
-      </c>
-      <c r="B966" t="s">
-        <v>1849</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B967" t="s">
         <v>1850</v>
-      </c>
-      <c r="B967" t="s">
-        <v>1851</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B968" t="s">
         <v>1852</v>
-      </c>
-      <c r="B968" t="s">
-        <v>1853</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B969" t="s">
         <v>1854</v>
-      </c>
-      <c r="B969" t="s">
-        <v>1855</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B970" t="s">
         <v>1856</v>
-      </c>
-      <c r="B970" t="s">
-        <v>1857</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B971" t="s">
         <v>1858</v>
-      </c>
-      <c r="B971" t="s">
-        <v>1859</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B972" t="s">
         <v>1860</v>
-      </c>
-      <c r="B972" t="s">
-        <v>1861</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B973" t="s">
         <v>1862</v>
-      </c>
-      <c r="B973" t="s">
-        <v>1863</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B974" t="s">
         <v>1864</v>
-      </c>
-      <c r="B974" t="s">
-        <v>1865</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B975" t="s">
         <v>1866</v>
-      </c>
-      <c r="B975" t="s">
-        <v>1867</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B976" t="s">
         <v>1868</v>
-      </c>
-      <c r="B976" t="s">
-        <v>1869</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B977" t="s">
         <v>1870</v>
-      </c>
-      <c r="B977" t="s">
-        <v>1871</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B978" t="s">
         <v>1872</v>
-      </c>
-      <c r="B978" t="s">
-        <v>1873</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B979" t="s">
         <v>1874</v>
-      </c>
-      <c r="B979" t="s">
-        <v>1875</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B980" t="s">
         <v>1876</v>
-      </c>
-      <c r="B980" t="s">
-        <v>1877</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B981" t="s">
         <v>1878</v>
-      </c>
-      <c r="B981" t="s">
-        <v>1879</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B982" t="s">
         <v>1880</v>
-      </c>
-      <c r="B982" t="s">
-        <v>1881</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B983" t="s">
         <v>1882</v>
-      </c>
-      <c r="B983" t="s">
-        <v>1883</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B984" t="s">
         <v>1884</v>
-      </c>
-      <c r="B984" t="s">
-        <v>1885</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B985" t="s">
         <v>1886</v>
-      </c>
-      <c r="B985" t="s">
-        <v>1887</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B986" t="s">
         <v>1888</v>
-      </c>
-      <c r="B986" t="s">
-        <v>1889</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B987" t="s">
         <v>1890</v>
-      </c>
-      <c r="B987" t="s">
-        <v>1891</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B988" t="s">
         <v>1892</v>
-      </c>
-      <c r="B988" t="s">
-        <v>1893</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B989" t="s">
         <v>1894</v>
-      </c>
-      <c r="B989" t="s">
-        <v>1895</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B990" t="s">
         <v>1896</v>
@@ -15132,228 +15135,228 @@
         <v>1897</v>
       </c>
       <c r="B991" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B992" t="s">
         <v>1899</v>
-      </c>
-      <c r="B992" t="s">
-        <v>1900</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B993" t="s">
         <v>1901</v>
-      </c>
-      <c r="B993" t="s">
-        <v>1902</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B994" t="s">
         <v>1903</v>
-      </c>
-      <c r="B994" t="s">
-        <v>1904</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B995" t="s">
         <v>1905</v>
-      </c>
-      <c r="B995" t="s">
-        <v>1906</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B996" t="s">
         <v>1907</v>
-      </c>
-      <c r="B996" t="s">
-        <v>1908</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B997" t="s">
         <v>1909</v>
-      </c>
-      <c r="B997" t="s">
-        <v>1910</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B998" t="s">
         <v>1911</v>
-      </c>
-      <c r="B998" t="s">
-        <v>1912</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B999" t="s">
         <v>1913</v>
-      </c>
-      <c r="B999" t="s">
-        <v>1914</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B1000" t="s">
         <v>1915</v>
-      </c>
-      <c r="B1000" t="s">
-        <v>1916</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
+        <v>1916</v>
+      </c>
+      <c r="B1001" t="s">
         <v>1917</v>
-      </c>
-      <c r="B1001" t="s">
-        <v>1918</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B1002" t="s">
         <v>1919</v>
-      </c>
-      <c r="B1002" t="s">
-        <v>1920</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B1003" t="s">
         <v>1921</v>
-      </c>
-      <c r="B1003" t="s">
-        <v>1922</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
+        <v>1922</v>
+      </c>
+      <c r="B1004" t="s">
         <v>1923</v>
-      </c>
-      <c r="B1004" t="s">
-        <v>1924</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B1005" t="s">
         <v>1925</v>
-      </c>
-      <c r="B1005" t="s">
-        <v>1926</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
+        <v>1926</v>
+      </c>
+      <c r="B1006" t="s">
         <v>1927</v>
-      </c>
-      <c r="B1006" t="s">
-        <v>1928</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B1007" t="s">
         <v>1929</v>
-      </c>
-      <c r="B1007" t="s">
-        <v>1930</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B1008" t="s">
         <v>1931</v>
-      </c>
-      <c r="B1008" t="s">
-        <v>1932</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B1009" t="s">
         <v>1933</v>
-      </c>
-      <c r="B1009" t="s">
-        <v>1934</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B1010" t="s">
         <v>1935</v>
-      </c>
-      <c r="B1010" t="s">
-        <v>1936</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B1011" t="s">
         <v>1937</v>
-      </c>
-      <c r="B1011" t="s">
-        <v>1938</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B1012" t="s">
         <v>1939</v>
-      </c>
-      <c r="B1012" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B1013" t="s">
         <v>1941</v>
-      </c>
-      <c r="B1013" t="s">
-        <v>1942</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B1014" t="s">
         <v>1943</v>
-      </c>
-      <c r="B1014" t="s">
-        <v>1944</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B1015" t="s">
         <v>1945</v>
-      </c>
-      <c r="B1015" t="s">
-        <v>1946</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B1016" t="s">
         <v>1947</v>
-      </c>
-      <c r="B1016" t="s">
-        <v>1948</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B1017" t="s">
         <v>1949</v>
-      </c>
-      <c r="B1017" t="s">
-        <v>1950</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B1018" t="s">
         <v>1951</v>
-      </c>
-      <c r="B1018" t="s">
-        <v>1952</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="B1019" t="s">
         <v>1953</v>
@@ -15364,44 +15367,44 @@
         <v>1954</v>
       </c>
       <c r="B1020" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B1021" t="s">
         <v>1956</v>
-      </c>
-      <c r="B1021" t="s">
-        <v>1957</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B1022" t="s">
         <v>1958</v>
-      </c>
-      <c r="B1022" t="s">
-        <v>1959</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B1023" t="s">
         <v>1960</v>
-      </c>
-      <c r="B1023" t="s">
-        <v>1961</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B1024" t="s">
         <v>1962</v>
-      </c>
-      <c r="B1024" t="s">
-        <v>1963</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B1025" t="s">
         <v>1964</v>
@@ -15412,84 +15415,84 @@
         <v>1965</v>
       </c>
       <c r="B1026" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B1027" t="s">
         <v>1967</v>
-      </c>
-      <c r="B1027" t="s">
-        <v>1968</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B1028" t="s">
         <v>1969</v>
-      </c>
-      <c r="B1028" t="s">
-        <v>1970</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B1029" t="s">
         <v>1971</v>
-      </c>
-      <c r="B1029" t="s">
-        <v>1972</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
+        <v>1972</v>
+      </c>
+      <c r="B1030" t="s">
         <v>1973</v>
-      </c>
-      <c r="B1030" t="s">
-        <v>1974</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
+        <v>1974</v>
+      </c>
+      <c r="B1031" t="s">
         <v>1975</v>
-      </c>
-      <c r="B1031" t="s">
-        <v>1976</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B1032" t="s">
         <v>1977</v>
-      </c>
-      <c r="B1032" t="s">
-        <v>1978</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
+        <v>1978</v>
+      </c>
+      <c r="B1033" t="s">
         <v>1979</v>
-      </c>
-      <c r="B1033" t="s">
-        <v>1980</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B1034" t="s">
         <v>1981</v>
-      </c>
-      <c r="B1034" t="s">
-        <v>1982</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B1035" t="s">
         <v>1983</v>
-      </c>
-      <c r="B1035" t="s">
-        <v>1984</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="B1036" t="s">
         <v>1985</v>
@@ -15500,364 +15503,364 @@
         <v>1986</v>
       </c>
       <c r="B1037" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B1038" t="s">
         <v>1988</v>
-      </c>
-      <c r="B1038" t="s">
-        <v>1989</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B1039" t="s">
         <v>1990</v>
-      </c>
-      <c r="B1039" t="s">
-        <v>1991</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B1040" t="s">
         <v>1992</v>
-      </c>
-      <c r="B1040" t="s">
-        <v>1993</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B1041" t="s">
         <v>1994</v>
-      </c>
-      <c r="B1041" t="s">
-        <v>1995</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B1042" t="s">
         <v>1996</v>
-      </c>
-      <c r="B1042" t="s">
-        <v>1997</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B1043" t="s">
         <v>1998</v>
-      </c>
-      <c r="B1043" t="s">
-        <v>1999</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1044" t="s">
         <v>2000</v>
-      </c>
-      <c r="B1044" t="s">
-        <v>2001</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B1045" t="s">
         <v>2002</v>
-      </c>
-      <c r="B1045" t="s">
-        <v>2003</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1046" t="s">
         <v>2004</v>
-      </c>
-      <c r="B1046" t="s">
-        <v>2005</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B1047" t="s">
         <v>2006</v>
-      </c>
-      <c r="B1047" t="s">
-        <v>2007</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B1048" t="s">
         <v>2008</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>2009</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B1049" t="s">
         <v>2010</v>
-      </c>
-      <c r="B1049" t="s">
-        <v>2011</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B1050" t="s">
         <v>2012</v>
-      </c>
-      <c r="B1050" t="s">
-        <v>2013</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B1051" t="s">
         <v>2014</v>
-      </c>
-      <c r="B1051" t="s">
-        <v>2015</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1052" t="s">
         <v>2016</v>
-      </c>
-      <c r="B1052" t="s">
-        <v>2017</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B1053" t="s">
         <v>2018</v>
-      </c>
-      <c r="B1053" t="s">
-        <v>2019</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B1054" t="s">
         <v>2020</v>
-      </c>
-      <c r="B1054" t="s">
-        <v>2021</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B1055" t="s">
         <v>2022</v>
-      </c>
-      <c r="B1055" t="s">
-        <v>2023</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B1056" t="s">
         <v>2024</v>
-      </c>
-      <c r="B1056" t="s">
-        <v>2025</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B1057" t="s">
         <v>2026</v>
-      </c>
-      <c r="B1057" t="s">
-        <v>2027</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B1058" t="s">
         <v>2028</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>2029</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
+        <v>2029</v>
+      </c>
+      <c r="B1059" t="s">
         <v>2030</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>2031</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
+        <v>2031</v>
+      </c>
+      <c r="B1060" t="s">
         <v>2032</v>
-      </c>
-      <c r="B1060" t="s">
-        <v>2033</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B1061" t="s">
         <v>2034</v>
-      </c>
-      <c r="B1061" t="s">
-        <v>2035</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B1062" t="s">
         <v>2036</v>
-      </c>
-      <c r="B1062" t="s">
-        <v>2037</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B1063" t="s">
         <v>2038</v>
-      </c>
-      <c r="B1063" t="s">
-        <v>2039</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B1064" t="s">
         <v>2040</v>
-      </c>
-      <c r="B1064" t="s">
-        <v>2041</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B1065" t="s">
         <v>2042</v>
-      </c>
-      <c r="B1065" t="s">
-        <v>2043</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B1066" t="s">
         <v>2044</v>
-      </c>
-      <c r="B1066" t="s">
-        <v>2045</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B1067" t="s">
         <v>2046</v>
-      </c>
-      <c r="B1067" t="s">
-        <v>2047</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B1068" t="s">
         <v>2048</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>2049</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B1069" t="s">
         <v>2050</v>
-      </c>
-      <c r="B1069" t="s">
-        <v>2051</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B1070" t="s">
         <v>2052</v>
-      </c>
-      <c r="B1070" t="s">
-        <v>2053</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B1071" t="s">
         <v>2054</v>
-      </c>
-      <c r="B1071" t="s">
-        <v>2055</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B1072" t="s">
         <v>2056</v>
-      </c>
-      <c r="B1072" t="s">
-        <v>2057</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B1073" t="s">
         <v>2058</v>
-      </c>
-      <c r="B1073" t="s">
-        <v>2059</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B1074" t="s">
         <v>2060</v>
-      </c>
-      <c r="B1074" t="s">
-        <v>2061</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B1075" t="s">
         <v>2062</v>
-      </c>
-      <c r="B1075" t="s">
-        <v>2063</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B1076" t="s">
         <v>2064</v>
-      </c>
-      <c r="B1076" t="s">
-        <v>2065</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B1077" t="s">
         <v>2066</v>
-      </c>
-      <c r="B1077" t="s">
-        <v>2067</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B1078" t="s">
         <v>2068</v>
-      </c>
-      <c r="B1078" t="s">
-        <v>2069</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B1079" t="s">
         <v>2070</v>
-      </c>
-      <c r="B1079" t="s">
-        <v>2071</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B1080" t="s">
         <v>2072</v>
-      </c>
-      <c r="B1080" t="s">
-        <v>2073</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B1081" t="s">
         <v>2074</v>
-      </c>
-      <c r="B1081" t="s">
-        <v>2075</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="B1082" t="s">
         <v>2076</v>
@@ -15868,212 +15871,212 @@
         <v>2077</v>
       </c>
       <c r="B1083" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B1084" t="s">
         <v>2079</v>
-      </c>
-      <c r="B1084" t="s">
-        <v>2080</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B1085" t="s">
         <v>2081</v>
-      </c>
-      <c r="B1085" t="s">
-        <v>2082</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B1086" t="s">
         <v>2083</v>
-      </c>
-      <c r="B1086" t="s">
-        <v>2084</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
+        <v>2084</v>
+      </c>
+      <c r="B1087" t="s">
         <v>2085</v>
-      </c>
-      <c r="B1087" t="s">
-        <v>2086</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B1088" t="s">
         <v>2087</v>
-      </c>
-      <c r="B1088" t="s">
-        <v>2088</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
+        <v>2088</v>
+      </c>
+      <c r="B1089" t="s">
         <v>2089</v>
-      </c>
-      <c r="B1089" t="s">
-        <v>2090</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B1090" t="s">
         <v>2091</v>
-      </c>
-      <c r="B1090" t="s">
-        <v>2092</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B1091" t="s">
         <v>2093</v>
-      </c>
-      <c r="B1091" t="s">
-        <v>2094</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B1092" t="s">
         <v>2095</v>
-      </c>
-      <c r="B1092" t="s">
-        <v>2096</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B1093" t="s">
         <v>2097</v>
-      </c>
-      <c r="B1093" t="s">
-        <v>2098</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
+        <v>2098</v>
+      </c>
+      <c r="B1094" t="s">
         <v>2099</v>
-      </c>
-      <c r="B1094" t="s">
-        <v>2100</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B1095" t="s">
         <v>2101</v>
-      </c>
-      <c r="B1095" t="s">
-        <v>2102</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B1096" t="s">
         <v>2103</v>
-      </c>
-      <c r="B1096" t="s">
-        <v>2104</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B1097" t="s">
         <v>2105</v>
-      </c>
-      <c r="B1097" t="s">
-        <v>2106</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B1098" t="s">
         <v>2107</v>
-      </c>
-      <c r="B1098" t="s">
-        <v>2108</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B1099" t="s">
         <v>2109</v>
-      </c>
-      <c r="B1099" t="s">
-        <v>2110</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B1100" t="s">
         <v>2111</v>
-      </c>
-      <c r="B1100" t="s">
-        <v>2112</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B1101" t="s">
         <v>2113</v>
-      </c>
-      <c r="B1101" t="s">
-        <v>2114</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B1102" t="s">
         <v>2115</v>
-      </c>
-      <c r="B1102" t="s">
-        <v>2116</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B1103" t="s">
         <v>2117</v>
-      </c>
-      <c r="B1103" t="s">
-        <v>2118</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B1104" t="s">
         <v>2119</v>
-      </c>
-      <c r="B1104" t="s">
-        <v>2120</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B1105" t="s">
         <v>2121</v>
-      </c>
-      <c r="B1105" t="s">
-        <v>2122</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B1106" t="s">
         <v>2123</v>
-      </c>
-      <c r="B1106" t="s">
-        <v>2124</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B1107" t="s">
         <v>2125</v>
-      </c>
-      <c r="B1107" t="s">
-        <v>2126</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B1108" t="s">
         <v>2127</v>
-      </c>
-      <c r="B1108" t="s">
-        <v>2128</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="B1109" t="s">
         <v>2129</v>
@@ -16084,68 +16087,68 @@
         <v>2130</v>
       </c>
       <c r="B1110" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
+        <v>2131</v>
+      </c>
+      <c r="B1111" t="s">
         <v>2132</v>
-      </c>
-      <c r="B1111" t="s">
-        <v>2133</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B1112" t="s">
         <v>2134</v>
-      </c>
-      <c r="B1112" t="s">
-        <v>2135</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B1113" t="s">
         <v>2136</v>
-      </c>
-      <c r="B1113" t="s">
-        <v>2137</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B1114" t="s">
         <v>2138</v>
-      </c>
-      <c r="B1114" t="s">
-        <v>2139</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B1115" t="s">
         <v>2140</v>
-      </c>
-      <c r="B1115" t="s">
-        <v>2141</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B1116" t="s">
         <v>2142</v>
-      </c>
-      <c r="B1116" t="s">
-        <v>2143</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B1117" t="s">
         <v>2144</v>
-      </c>
-      <c r="B1117" t="s">
-        <v>2145</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="B1118" t="s">
         <v>2146</v>
@@ -16156,220 +16159,220 @@
         <v>2147</v>
       </c>
       <c r="B1119" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B1120" t="s">
         <v>2149</v>
-      </c>
-      <c r="B1120" t="s">
-        <v>2150</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B1121" t="s">
         <v>2151</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>2152</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B1122" t="s">
         <v>2153</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>2154</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B1123" t="s">
         <v>2155</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>2156</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B1124" t="s">
         <v>2157</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>2158</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>2158</v>
+      </c>
+      <c r="B1125" t="s">
         <v>2159</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>2160</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B1126" t="s">
         <v>2161</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>2162</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B1127" t="s">
         <v>2163</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>2164</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B1128" t="s">
         <v>2165</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>2166</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B1129" t="s">
         <v>2167</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>2168</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B1130" t="s">
         <v>2169</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>2170</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B1131" t="s">
         <v>2171</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>2172</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B1132" t="s">
         <v>2173</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B1133" t="s">
         <v>2175</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>2176</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B1134" t="s">
         <v>2177</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>2178</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B1135" t="s">
         <v>2179</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>2180</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
+        <v>2180</v>
+      </c>
+      <c r="B1136" t="s">
         <v>2181</v>
-      </c>
-      <c r="B1136" t="s">
-        <v>2182</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B1137" t="s">
         <v>2183</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>2184</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B1138" t="s">
         <v>2185</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>2186</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B1139" t="s">
         <v>2187</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>2188</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B1140" t="s">
         <v>2189</v>
-      </c>
-      <c r="B1140" t="s">
-        <v>2190</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1141" t="s">
         <v>2191</v>
-      </c>
-      <c r="B1141" t="s">
-        <v>2192</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B1142" t="s">
         <v>2193</v>
-      </c>
-      <c r="B1142" t="s">
-        <v>2194</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B1143" t="s">
         <v>2195</v>
-      </c>
-      <c r="B1143" t="s">
-        <v>2196</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B1144" t="s">
         <v>2197</v>
-      </c>
-      <c r="B1144" t="s">
-        <v>2198</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B1145" t="s">
         <v>2199</v>
-      </c>
-      <c r="B1145" t="s">
-        <v>2200</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="B1146" t="s">
         <v>2201</v>
@@ -16380,124 +16383,124 @@
         <v>2202</v>
       </c>
       <c r="B1147" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B1148" t="s">
         <v>2204</v>
-      </c>
-      <c r="B1148" t="s">
-        <v>2205</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
+        <v>2205</v>
+      </c>
+      <c r="B1149" t="s">
         <v>2206</v>
-      </c>
-      <c r="B1149" t="s">
-        <v>2207</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B1150" t="s">
         <v>2208</v>
-      </c>
-      <c r="B1150" t="s">
-        <v>2209</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B1151" t="s">
         <v>2210</v>
-      </c>
-      <c r="B1151" t="s">
-        <v>2211</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
+        <v>2211</v>
+      </c>
+      <c r="B1152" t="s">
         <v>2212</v>
-      </c>
-      <c r="B1152" t="s">
-        <v>2213</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B1153" t="s">
         <v>2214</v>
-      </c>
-      <c r="B1153" t="s">
-        <v>2215</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B1154" t="s">
         <v>2216</v>
-      </c>
-      <c r="B1154" t="s">
-        <v>2217</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B1155" t="s">
         <v>2218</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>2219</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>2219</v>
+      </c>
+      <c r="B1156" t="s">
         <v>2220</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>2221</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
+        <v>2221</v>
+      </c>
+      <c r="B1157" t="s">
         <v>2222</v>
-      </c>
-      <c r="B1157" t="s">
-        <v>2223</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
+        <v>2223</v>
+      </c>
+      <c r="B1158" t="s">
         <v>2224</v>
-      </c>
-      <c r="B1158" t="s">
-        <v>2225</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
+        <v>2225</v>
+      </c>
+      <c r="B1159" t="s">
         <v>2226</v>
-      </c>
-      <c r="B1159" t="s">
-        <v>2227</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1160" t="s">
         <v>2228</v>
-      </c>
-      <c r="B1160" t="s">
-        <v>2229</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B1161" t="s">
         <v>2230</v>
-      </c>
-      <c r="B1161" t="s">
-        <v>2231</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="B1162" t="s">
         <v>2232</v>
@@ -16508,20 +16511,20 @@
         <v>2233</v>
       </c>
       <c r="B1163" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B1164" t="s">
         <v>2235</v>
-      </c>
-      <c r="B1164" t="s">
-        <v>2236</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="B1165" t="s">
         <v>2237</v>
@@ -16532,20 +16535,20 @@
         <v>2238</v>
       </c>
       <c r="B1166" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B1167" t="s">
         <v>2240</v>
-      </c>
-      <c r="B1167" t="s">
-        <v>2241</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="B1168" t="s">
         <v>2242</v>
@@ -16556,12 +16559,12 @@
         <v>2243</v>
       </c>
       <c r="B1169" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="B1170" t="s">
         <v>2245</v>
@@ -16572,44 +16575,44 @@
         <v>2246</v>
       </c>
       <c r="B1171" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
+        <v>2247</v>
+      </c>
+      <c r="B1172" t="s">
         <v>2248</v>
-      </c>
-      <c r="B1172" t="s">
-        <v>2249</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
+        <v>2249</v>
+      </c>
+      <c r="B1173" t="s">
         <v>2250</v>
-      </c>
-      <c r="B1173" t="s">
-        <v>2251</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
+        <v>2251</v>
+      </c>
+      <c r="B1174" t="s">
         <v>2252</v>
-      </c>
-      <c r="B1174" t="s">
-        <v>2253</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
+        <v>2253</v>
+      </c>
+      <c r="B1175" t="s">
         <v>2254</v>
-      </c>
-      <c r="B1175" t="s">
-        <v>2255</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="B1176" t="s">
         <v>2256</v>
@@ -16620,12 +16623,12 @@
         <v>2257</v>
       </c>
       <c r="B1177" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="B1178" t="s">
         <v>2259</v>
@@ -16636,63 +16639,63 @@
         <v>2260</v>
       </c>
       <c r="B1179" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B1180" t="s">
         <v>2262</v>
-      </c>
-      <c r="B1180" t="s">
-        <v>2263</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B1181" t="s">
         <v>2264</v>
-      </c>
-      <c r="B1181" t="s">
-        <v>2265</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B1182" t="s">
         <v>2266</v>
-      </c>
-      <c r="B1182" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
+        <v>2267</v>
+      </c>
+      <c r="B1183" t="s">
         <v>2268</v>
-      </c>
-      <c r="B1183" t="s">
-        <v>2269</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
+        <v>2269</v>
+      </c>
+      <c r="B1184" t="s">
         <v>2270</v>
-      </c>
-      <c r="B1184" t="s">
-        <v>2271</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
+        <v>2271</v>
+      </c>
+      <c r="B1185" t="s">
         <v>2272</v>
-      </c>
-      <c r="B1185" t="s">
-        <v>2273</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B1186" t="s">
         <v>2274</v>
-      </c>
-      <c r="B1186" t="s">
-        <v>2135</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
@@ -16700,19 +16703,27 @@
         <v>2275</v>
       </c>
       <c r="B1187" t="s">
-        <v>2276</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B1188" t="s">
         <v>2277</v>
       </c>
-      <c r="B1188" t="s">
+    </row>
+    <row r="1189" spans="1:2">
+      <c r="A1189" t="s">
         <v>2278</v>
       </c>
+      <c r="B1189" t="s">
+        <v>2279</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1188"/>
+  <autoFilter ref="A1:B1189"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ko/headTags.xlsx
+++ b/lang/ko/headTags.xlsx
@@ -1858,6 +1858,12 @@
     <t>동화</t>
   </si>
   <si>
+    <t>Fall Drop</t>
+  </si>
+  <si>
+    <t>가을 낙하</t>
+  </si>
+  <si>
     <t>Fall Guys</t>
   </si>
   <si>
@@ -6851,12 +6857,6 @@
   </si>
   <si>
     <t>하이픽셀(돌연변이) 태그</t>
-  </si>
-  <si>
-    <t>Fall Drop</t>
-  </si>
-  <si>
-    <t>가을 낙하</t>
   </si>
 </sst>
 </file>
@@ -9815,12 +9815,12 @@
         <v>615</v>
       </c>
       <c r="B326" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B327" t="s">
         <v>617</v>
@@ -10663,12 +10663,12 @@
         <v>826</v>
       </c>
       <c r="B432" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="433" spans="1:2">
       <c r="A433" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B433" t="s">
         <v>828</v>
@@ -10687,12 +10687,12 @@
         <v>831</v>
       </c>
       <c r="B435" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B436" t="s">
         <v>833</v>
@@ -10735,12 +10735,12 @@
         <v>842</v>
       </c>
       <c r="B441" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B442" t="s">
         <v>844</v>
@@ -10751,12 +10751,12 @@
         <v>845</v>
       </c>
       <c r="B443" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="444" spans="1:2">
       <c r="A444" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B444" t="s">
         <v>847</v>
@@ -10847,12 +10847,12 @@
         <v>868</v>
       </c>
       <c r="B455" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="456" spans="1:2">
       <c r="A456" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B456" t="s">
         <v>870</v>
@@ -10967,15 +10967,15 @@
         <v>897</v>
       </c>
       <c r="B470" t="s">
-        <v>160</v>
+        <v>898</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B471" t="s">
-        <v>899</v>
+        <v>160</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -11071,20 +11071,20 @@
         <v>922</v>
       </c>
       <c r="B483" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B484" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B485" t="s">
         <v>925</v>
@@ -11319,12 +11319,12 @@
         <v>982</v>
       </c>
       <c r="B514" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B515" t="s">
         <v>984</v>
@@ -11487,12 +11487,12 @@
         <v>1023</v>
       </c>
       <c r="B535" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B536" t="s">
         <v>1025</v>
@@ -11527,12 +11527,12 @@
         <v>1032</v>
       </c>
       <c r="B540" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B541" t="s">
         <v>1034</v>
@@ -11759,12 +11759,12 @@
         <v>1089</v>
       </c>
       <c r="B569" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B570" t="s">
         <v>1091</v>
@@ -11831,12 +11831,12 @@
         <v>1106</v>
       </c>
       <c r="B578" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B579" t="s">
         <v>1108</v>
@@ -11999,12 +11999,12 @@
         <v>1147</v>
       </c>
       <c r="B599" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B600" t="s">
         <v>1149</v>
@@ -12183,12 +12183,12 @@
         <v>1192</v>
       </c>
       <c r="B622" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B623" t="s">
         <v>1194</v>
@@ -12207,23 +12207,23 @@
         <v>1197</v>
       </c>
       <c r="B625" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B626" t="s">
-        <v>870</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B627" t="s">
-        <v>1200</v>
+        <v>872</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -12367,12 +12367,12 @@
         <v>1235</v>
       </c>
       <c r="B645" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B646" t="s">
         <v>1237</v>
@@ -12463,12 +12463,12 @@
         <v>1258</v>
       </c>
       <c r="B657" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B658" t="s">
         <v>1260</v>
@@ -12655,12 +12655,12 @@
         <v>1305</v>
       </c>
       <c r="B681" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B682" t="s">
         <v>1307</v>
@@ -12719,12 +12719,12 @@
         <v>1320</v>
       </c>
       <c r="B689" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B690" t="s">
         <v>1322</v>
@@ -12855,12 +12855,12 @@
         <v>1353</v>
       </c>
       <c r="B706" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B707" t="s">
         <v>1355</v>
@@ -12943,12 +12943,12 @@
         <v>1374</v>
       </c>
       <c r="B717" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B718" t="s">
         <v>1376</v>
@@ -13103,12 +13103,12 @@
         <v>1413</v>
       </c>
       <c r="B737" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B738" t="s">
         <v>1415</v>
@@ -13559,20 +13559,20 @@
         <v>1526</v>
       </c>
       <c r="B794" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B795" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B796" t="s">
         <v>1529</v>
@@ -13583,12 +13583,12 @@
         <v>1530</v>
       </c>
       <c r="B797" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B798" t="s">
         <v>1532</v>
@@ -13615,12 +13615,12 @@
         <v>1537</v>
       </c>
       <c r="B801" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B802" t="s">
         <v>1539</v>
@@ -13647,12 +13647,12 @@
         <v>1544</v>
       </c>
       <c r="B805" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B806" t="s">
         <v>1546</v>
@@ -13663,12 +13663,12 @@
         <v>1547</v>
       </c>
       <c r="B807" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B808" t="s">
         <v>1549</v>
@@ -13911,36 +13911,36 @@
         <v>1608</v>
       </c>
       <c r="B838" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B839" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B840" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B841" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B842" t="s">
         <v>1613</v>
@@ -13983,12 +13983,12 @@
         <v>1622</v>
       </c>
       <c r="B847" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B848" t="s">
         <v>1624</v>
@@ -14239,12 +14239,12 @@
         <v>1685</v>
       </c>
       <c r="B879" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B880" t="s">
         <v>1687</v>
@@ -14311,20 +14311,20 @@
         <v>1702</v>
       </c>
       <c r="B888" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B889" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B890" t="s">
         <v>1705</v>
@@ -14367,12 +14367,12 @@
         <v>1714</v>
       </c>
       <c r="B895" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B896" t="s">
         <v>1716</v>
@@ -14503,20 +14503,20 @@
         <v>1747</v>
       </c>
       <c r="B912" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="B913" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B914" t="s">
         <v>1750</v>
@@ -14527,20 +14527,20 @@
         <v>1751</v>
       </c>
       <c r="B915" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B916" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B917" t="s">
         <v>1754</v>
@@ -14551,12 +14551,12 @@
         <v>1755</v>
       </c>
       <c r="B918" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="B919" t="s">
         <v>1757</v>
@@ -14607,12 +14607,12 @@
         <v>1768</v>
       </c>
       <c r="B925" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B926" t="s">
         <v>1770</v>
@@ -14687,12 +14687,12 @@
         <v>1787</v>
       </c>
       <c r="B935" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="B936" t="s">
         <v>1789</v>
@@ -14799,12 +14799,12 @@
         <v>1814</v>
       </c>
       <c r="B949" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B950" t="s">
         <v>1816</v>
@@ -15135,12 +15135,12 @@
         <v>1897</v>
       </c>
       <c r="B991" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B992" t="s">
         <v>1899</v>
@@ -15367,12 +15367,12 @@
         <v>1954</v>
       </c>
       <c r="B1020" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="B1021" t="s">
         <v>1956</v>
@@ -15415,12 +15415,12 @@
         <v>1965</v>
       </c>
       <c r="B1026" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="B1027" t="s">
         <v>1967</v>
@@ -15503,12 +15503,12 @@
         <v>1986</v>
       </c>
       <c r="B1037" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="B1038" t="s">
         <v>1988</v>
@@ -15871,12 +15871,12 @@
         <v>2077</v>
       </c>
       <c r="B1083" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="B1084" t="s">
         <v>2079</v>
@@ -16087,12 +16087,12 @@
         <v>2130</v>
       </c>
       <c r="B1110" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="B1111" t="s">
         <v>2132</v>
@@ -16159,12 +16159,12 @@
         <v>2147</v>
       </c>
       <c r="B1119" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="B1120" t="s">
         <v>2149</v>
@@ -16383,12 +16383,12 @@
         <v>2202</v>
       </c>
       <c r="B1147" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="B1148" t="s">
         <v>2204</v>
@@ -16511,12 +16511,12 @@
         <v>2233</v>
       </c>
       <c r="B1163" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="B1164" t="s">
         <v>2235</v>
@@ -16535,12 +16535,12 @@
         <v>2238</v>
       </c>
       <c r="B1166" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="B1167" t="s">
         <v>2240</v>
@@ -16559,12 +16559,12 @@
         <v>2243</v>
       </c>
       <c r="B1169" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="B1170" t="s">
         <v>2245</v>
@@ -16575,12 +16575,12 @@
         <v>2246</v>
       </c>
       <c r="B1171" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="B1172" t="s">
         <v>2248</v>
@@ -16623,12 +16623,12 @@
         <v>2257</v>
       </c>
       <c r="B1177" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="B1178" t="s">
         <v>2259</v>
@@ -16639,12 +16639,12 @@
         <v>2260</v>
       </c>
       <c r="B1179" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="B1180" t="s">
         <v>2262</v>
@@ -16703,15 +16703,15 @@
         <v>2275</v>
       </c>
       <c r="B1187" t="s">
-        <v>2136</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="B1188" t="s">
-        <v>2277</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="1189" spans="1:2">

--- a/lang/ko/headTags.xlsx
+++ b/lang/ko/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2282">
   <si>
     <t>en</t>
   </si>
@@ -5072,6 +5072,12 @@
   </si>
   <si>
     <t>프레데터</t>
+  </si>
+  <si>
+    <t>Prehistoric Creature</t>
+  </si>
+  <si>
+    <t>선사 시대의 생물</t>
   </si>
   <si>
     <t>Present</t>
@@ -7203,7 +7209,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1189"/>
+  <dimension ref="A1:B1190"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14247,12 +14253,12 @@
         <v>1687</v>
       </c>
       <c r="B880" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B881" t="s">
         <v>1689</v>
@@ -14319,20 +14325,20 @@
         <v>1704</v>
       </c>
       <c r="B889" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B890" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B891" t="s">
         <v>1707</v>
@@ -14375,12 +14381,12 @@
         <v>1716</v>
       </c>
       <c r="B896" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B897" t="s">
         <v>1718</v>
@@ -14511,20 +14517,20 @@
         <v>1749</v>
       </c>
       <c r="B913" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B914" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B915" t="s">
         <v>1752</v>
@@ -14535,20 +14541,20 @@
         <v>1753</v>
       </c>
       <c r="B916" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B917" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B918" t="s">
         <v>1756</v>
@@ -14559,12 +14565,12 @@
         <v>1757</v>
       </c>
       <c r="B919" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B920" t="s">
         <v>1759</v>
@@ -14615,12 +14621,12 @@
         <v>1770</v>
       </c>
       <c r="B926" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B927" t="s">
         <v>1772</v>
@@ -14695,12 +14701,12 @@
         <v>1789</v>
       </c>
       <c r="B936" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B937" t="s">
         <v>1791</v>
@@ -14807,12 +14813,12 @@
         <v>1816</v>
       </c>
       <c r="B950" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B951" t="s">
         <v>1818</v>
@@ -15143,12 +15149,12 @@
         <v>1899</v>
       </c>
       <c r="B992" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B993" t="s">
         <v>1901</v>
@@ -15375,12 +15381,12 @@
         <v>1956</v>
       </c>
       <c r="B1021" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="B1022" t="s">
         <v>1958</v>
@@ -15423,12 +15429,12 @@
         <v>1967</v>
       </c>
       <c r="B1027" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="B1028" t="s">
         <v>1969</v>
@@ -15511,12 +15517,12 @@
         <v>1988</v>
       </c>
       <c r="B1038" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="B1039" t="s">
         <v>1990</v>
@@ -15879,12 +15885,12 @@
         <v>2079</v>
       </c>
       <c r="B1084" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="B1085" t="s">
         <v>2081</v>
@@ -16095,12 +16101,12 @@
         <v>2132</v>
       </c>
       <c r="B1111" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="B1112" t="s">
         <v>2134</v>
@@ -16167,12 +16173,12 @@
         <v>2149</v>
       </c>
       <c r="B1120" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="B1121" t="s">
         <v>2151</v>
@@ -16391,12 +16397,12 @@
         <v>2204</v>
       </c>
       <c r="B1148" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="B1149" t="s">
         <v>2206</v>
@@ -16519,12 +16525,12 @@
         <v>2235</v>
       </c>
       <c r="B1164" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="B1165" t="s">
         <v>2237</v>
@@ -16543,12 +16549,12 @@
         <v>2240</v>
       </c>
       <c r="B1167" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="B1168" t="s">
         <v>2242</v>
@@ -16567,12 +16573,12 @@
         <v>2245</v>
       </c>
       <c r="B1170" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="B1171" t="s">
         <v>2247</v>
@@ -16583,12 +16589,12 @@
         <v>2248</v>
       </c>
       <c r="B1172" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="B1173" t="s">
         <v>2250</v>
@@ -16631,12 +16637,12 @@
         <v>2259</v>
       </c>
       <c r="B1178" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="B1179" t="s">
         <v>2261</v>
@@ -16647,12 +16653,12 @@
         <v>2262</v>
       </c>
       <c r="B1180" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="B1181" t="s">
         <v>2264</v>
@@ -16711,19 +16717,27 @@
         <v>2277</v>
       </c>
       <c r="B1188" t="s">
-        <v>2138</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="B1189" t="s">
-        <v>2279</v>
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:2">
+      <c r="A1190" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>2281</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1189"/>
+  <autoFilter ref="A1:B1190"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ko/headTags.xlsx
+++ b/lang/ko/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2284">
   <si>
     <t>en</t>
   </si>
@@ -398,6 +398,12 @@
   </si>
   <si>
     <t>백 투 더 퓨처</t>
+  </si>
+  <si>
+    <t>Backrooms (Movie)</t>
+  </si>
+  <si>
+    <t>백룸 (영화)</t>
   </si>
   <si>
     <t>Bag</t>
@@ -7209,7 +7215,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1190"/>
+  <dimension ref="A1:B1191"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -7789,28 +7795,28 @@
         <v>137</v>
       </c>
       <c r="B72" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B73" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B74" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B75" t="s">
         <v>141</v>
@@ -7885,12 +7891,12 @@
         <v>158</v>
       </c>
       <c r="B84" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B85" t="s">
         <v>160</v>
@@ -7949,12 +7955,12 @@
         <v>173</v>
       </c>
       <c r="B92" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B93" t="s">
         <v>175</v>
@@ -8013,12 +8019,12 @@
         <v>188</v>
       </c>
       <c r="B100" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B101" t="s">
         <v>190</v>
@@ -8061,12 +8067,12 @@
         <v>199</v>
       </c>
       <c r="B106" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B107" t="s">
         <v>201</v>
@@ -8077,12 +8083,12 @@
         <v>202</v>
       </c>
       <c r="B108" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B109" t="s">
         <v>204</v>
@@ -8109,20 +8115,20 @@
         <v>209</v>
       </c>
       <c r="B112" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B113" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B114" t="s">
         <v>212</v>
@@ -8141,12 +8147,12 @@
         <v>215</v>
       </c>
       <c r="B116" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B117" t="s">
         <v>217</v>
@@ -8253,20 +8259,20 @@
         <v>242</v>
       </c>
       <c r="B130" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B131" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B132" t="s">
         <v>245</v>
@@ -8317,12 +8323,12 @@
         <v>256</v>
       </c>
       <c r="B138" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B139" t="s">
         <v>258</v>
@@ -8333,12 +8339,12 @@
         <v>259</v>
       </c>
       <c r="B140" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B141" t="s">
         <v>261</v>
@@ -8357,12 +8363,12 @@
         <v>264</v>
       </c>
       <c r="B143" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B144" t="s">
         <v>266</v>
@@ -8581,12 +8587,12 @@
         <v>319</v>
       </c>
       <c r="B171" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B172" t="s">
         <v>321</v>
@@ -8845,12 +8851,12 @@
         <v>384</v>
       </c>
       <c r="B204" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B205" t="s">
         <v>386</v>
@@ -9069,12 +9075,12 @@
         <v>439</v>
       </c>
       <c r="B232" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B233" t="s">
         <v>441</v>
@@ -9165,12 +9171,12 @@
         <v>462</v>
       </c>
       <c r="B244" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B245" t="s">
         <v>464</v>
@@ -9349,12 +9355,12 @@
         <v>507</v>
       </c>
       <c r="B267" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B268" t="s">
         <v>509</v>
@@ -9397,12 +9403,12 @@
         <v>518</v>
       </c>
       <c r="B273" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B274" t="s">
         <v>520</v>
@@ -9461,12 +9467,12 @@
         <v>533</v>
       </c>
       <c r="B281" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B282" t="s">
         <v>535</v>
@@ -9541,12 +9547,12 @@
         <v>552</v>
       </c>
       <c r="B291" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B292" t="s">
         <v>554</v>
@@ -9589,20 +9595,20 @@
         <v>563</v>
       </c>
       <c r="B297" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B298" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B299" t="s">
         <v>566</v>
@@ -9701,12 +9707,12 @@
         <v>589</v>
       </c>
       <c r="B311" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B312" t="s">
         <v>591</v>
@@ -9773,28 +9779,28 @@
         <v>606</v>
       </c>
       <c r="B320" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B321" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B322" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B323" t="s">
         <v>610</v>
@@ -9829,12 +9835,12 @@
         <v>617</v>
       </c>
       <c r="B327" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B328" t="s">
         <v>619</v>
@@ -10677,12 +10683,12 @@
         <v>828</v>
       </c>
       <c r="B433" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B434" t="s">
         <v>830</v>
@@ -10701,12 +10707,12 @@
         <v>833</v>
       </c>
       <c r="B436" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B437" t="s">
         <v>835</v>
@@ -10749,12 +10755,12 @@
         <v>844</v>
       </c>
       <c r="B442" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="443" spans="1:2">
       <c r="A443" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B443" t="s">
         <v>846</v>
@@ -10765,12 +10771,12 @@
         <v>847</v>
       </c>
       <c r="B444" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="445" spans="1:2">
       <c r="A445" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B445" t="s">
         <v>849</v>
@@ -10861,12 +10867,12 @@
         <v>870</v>
       </c>
       <c r="B456" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B457" t="s">
         <v>872</v>
@@ -10981,15 +10987,15 @@
         <v>899</v>
       </c>
       <c r="B471" t="s">
-        <v>160</v>
+        <v>900</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B472" t="s">
-        <v>901</v>
+        <v>162</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -11085,20 +11091,20 @@
         <v>924</v>
       </c>
       <c r="B484" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B485" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B486" t="s">
         <v>927</v>
@@ -11333,12 +11339,12 @@
         <v>984</v>
       </c>
       <c r="B515" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="A516" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B516" t="s">
         <v>986</v>
@@ -11501,12 +11507,12 @@
         <v>1025</v>
       </c>
       <c r="B536" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B537" t="s">
         <v>1027</v>
@@ -11541,12 +11547,12 @@
         <v>1034</v>
       </c>
       <c r="B541" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B542" t="s">
         <v>1036</v>
@@ -11773,12 +11779,12 @@
         <v>1091</v>
       </c>
       <c r="B570" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B571" t="s">
         <v>1093</v>
@@ -11845,12 +11851,12 @@
         <v>1108</v>
       </c>
       <c r="B579" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B580" t="s">
         <v>1110</v>
@@ -12013,12 +12019,12 @@
         <v>1149</v>
       </c>
       <c r="B600" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B601" t="s">
         <v>1151</v>
@@ -12197,12 +12203,12 @@
         <v>1194</v>
       </c>
       <c r="B623" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B624" t="s">
         <v>1196</v>
@@ -12221,23 +12227,23 @@
         <v>1199</v>
       </c>
       <c r="B626" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B627" t="s">
-        <v>872</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B628" t="s">
-        <v>1202</v>
+        <v>874</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -12381,12 +12387,12 @@
         <v>1237</v>
       </c>
       <c r="B646" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B647" t="s">
         <v>1239</v>
@@ -12477,12 +12483,12 @@
         <v>1260</v>
       </c>
       <c r="B658" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B659" t="s">
         <v>1262</v>
@@ -12669,12 +12675,12 @@
         <v>1307</v>
       </c>
       <c r="B682" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B683" t="s">
         <v>1309</v>
@@ -12733,12 +12739,12 @@
         <v>1322</v>
       </c>
       <c r="B690" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B691" t="s">
         <v>1324</v>
@@ -12869,12 +12875,12 @@
         <v>1355</v>
       </c>
       <c r="B707" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B708" t="s">
         <v>1357</v>
@@ -12957,12 +12963,12 @@
         <v>1376</v>
       </c>
       <c r="B718" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B719" t="s">
         <v>1378</v>
@@ -13117,12 +13123,12 @@
         <v>1415</v>
       </c>
       <c r="B738" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B739" t="s">
         <v>1417</v>
@@ -13573,20 +13579,20 @@
         <v>1528</v>
       </c>
       <c r="B795" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B796" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B797" t="s">
         <v>1531</v>
@@ -13597,12 +13603,12 @@
         <v>1532</v>
       </c>
       <c r="B798" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B799" t="s">
         <v>1534</v>
@@ -13629,12 +13635,12 @@
         <v>1539</v>
       </c>
       <c r="B802" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B803" t="s">
         <v>1541</v>
@@ -13661,12 +13667,12 @@
         <v>1546</v>
       </c>
       <c r="B806" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B807" t="s">
         <v>1548</v>
@@ -13677,12 +13683,12 @@
         <v>1549</v>
       </c>
       <c r="B808" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B809" t="s">
         <v>1551</v>
@@ -13925,36 +13931,36 @@
         <v>1610</v>
       </c>
       <c r="B839" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B840" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B841" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B842" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B843" t="s">
         <v>1615</v>
@@ -13997,12 +14003,12 @@
         <v>1624</v>
       </c>
       <c r="B848" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B849" t="s">
         <v>1626</v>
@@ -14261,12 +14267,12 @@
         <v>1689</v>
       </c>
       <c r="B881" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B882" t="s">
         <v>1691</v>
@@ -14333,20 +14339,20 @@
         <v>1706</v>
       </c>
       <c r="B890" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B891" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B892" t="s">
         <v>1709</v>
@@ -14389,12 +14395,12 @@
         <v>1718</v>
       </c>
       <c r="B897" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B898" t="s">
         <v>1720</v>
@@ -14525,20 +14531,20 @@
         <v>1751</v>
       </c>
       <c r="B914" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B915" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B916" t="s">
         <v>1754</v>
@@ -14549,20 +14555,20 @@
         <v>1755</v>
       </c>
       <c r="B917" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="B918" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="B919" t="s">
         <v>1758</v>
@@ -14573,12 +14579,12 @@
         <v>1759</v>
       </c>
       <c r="B920" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B921" t="s">
         <v>1761</v>
@@ -14629,12 +14635,12 @@
         <v>1772</v>
       </c>
       <c r="B927" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="B928" t="s">
         <v>1774</v>
@@ -14709,12 +14715,12 @@
         <v>1791</v>
       </c>
       <c r="B937" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B938" t="s">
         <v>1793</v>
@@ -14821,12 +14827,12 @@
         <v>1818</v>
       </c>
       <c r="B951" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B952" t="s">
         <v>1820</v>
@@ -15157,12 +15163,12 @@
         <v>1901</v>
       </c>
       <c r="B993" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B994" t="s">
         <v>1903</v>
@@ -15389,12 +15395,12 @@
         <v>1958</v>
       </c>
       <c r="B1022" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="B1023" t="s">
         <v>1960</v>
@@ -15437,12 +15443,12 @@
         <v>1969</v>
       </c>
       <c r="B1028" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="B1029" t="s">
         <v>1971</v>
@@ -15525,12 +15531,12 @@
         <v>1990</v>
       </c>
       <c r="B1039" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="B1040" t="s">
         <v>1992</v>
@@ -15893,12 +15899,12 @@
         <v>2081</v>
       </c>
       <c r="B1085" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="B1086" t="s">
         <v>2083</v>
@@ -16109,12 +16115,12 @@
         <v>2134</v>
       </c>
       <c r="B1112" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="B1113" t="s">
         <v>2136</v>
@@ -16181,12 +16187,12 @@
         <v>2151</v>
       </c>
       <c r="B1121" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="B1122" t="s">
         <v>2153</v>
@@ -16405,12 +16411,12 @@
         <v>2206</v>
       </c>
       <c r="B1149" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="B1150" t="s">
         <v>2208</v>
@@ -16533,12 +16539,12 @@
         <v>2237</v>
       </c>
       <c r="B1165" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="B1166" t="s">
         <v>2239</v>
@@ -16557,12 +16563,12 @@
         <v>2242</v>
       </c>
       <c r="B1168" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="B1169" t="s">
         <v>2244</v>
@@ -16581,12 +16587,12 @@
         <v>2247</v>
       </c>
       <c r="B1171" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="B1172" t="s">
         <v>2249</v>
@@ -16597,12 +16603,12 @@
         <v>2250</v>
       </c>
       <c r="B1173" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="B1174" t="s">
         <v>2252</v>
@@ -16645,12 +16651,12 @@
         <v>2261</v>
       </c>
       <c r="B1179" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="B1180" t="s">
         <v>2263</v>
@@ -16661,12 +16667,12 @@
         <v>2264</v>
       </c>
       <c r="B1181" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="B1182" t="s">
         <v>2266</v>
@@ -16725,19 +16731,27 @@
         <v>2279</v>
       </c>
       <c r="B1189" t="s">
-        <v>2140</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="B1190" t="s">
-        <v>2281</v>
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:2">
+      <c r="A1191" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>2283</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1190"/>
+  <autoFilter ref="A1:B1191"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ko/headTags.xlsx
+++ b/lang/ko/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2286">
   <si>
     <t>en</t>
   </si>
@@ -1472,6 +1472,12 @@
   </si>
   <si>
     <t>디아블로</t>
+  </si>
+  <si>
+    <t>Die of Death</t>
+  </si>
+  <si>
+    <t>죽음의 주사위</t>
   </si>
   <si>
     <t>Digimon</t>
@@ -7215,7 +7221,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1191"/>
+  <dimension ref="A1:B1192"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -9363,12 +9369,12 @@
         <v>509</v>
       </c>
       <c r="B268" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B269" t="s">
         <v>511</v>
@@ -9411,12 +9417,12 @@
         <v>520</v>
       </c>
       <c r="B274" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B275" t="s">
         <v>522</v>
@@ -9475,12 +9481,12 @@
         <v>535</v>
       </c>
       <c r="B282" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B283" t="s">
         <v>537</v>
@@ -9555,12 +9561,12 @@
         <v>554</v>
       </c>
       <c r="B292" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B293" t="s">
         <v>556</v>
@@ -9603,20 +9609,20 @@
         <v>565</v>
       </c>
       <c r="B298" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B299" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="300" spans="1:2">
       <c r="A300" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B300" t="s">
         <v>568</v>
@@ -9715,12 +9721,12 @@
         <v>591</v>
       </c>
       <c r="B312" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B313" t="s">
         <v>593</v>
@@ -9787,28 +9793,28 @@
         <v>608</v>
       </c>
       <c r="B321" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B322" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B323" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B324" t="s">
         <v>612</v>
@@ -9843,12 +9849,12 @@
         <v>619</v>
       </c>
       <c r="B328" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B329" t="s">
         <v>621</v>
@@ -10691,12 +10697,12 @@
         <v>830</v>
       </c>
       <c r="B434" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B435" t="s">
         <v>832</v>
@@ -10715,12 +10721,12 @@
         <v>835</v>
       </c>
       <c r="B437" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B438" t="s">
         <v>837</v>
@@ -10763,12 +10769,12 @@
         <v>846</v>
       </c>
       <c r="B443" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="444" spans="1:2">
       <c r="A444" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B444" t="s">
         <v>848</v>
@@ -10779,12 +10785,12 @@
         <v>849</v>
       </c>
       <c r="B445" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="446" spans="1:2">
       <c r="A446" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B446" t="s">
         <v>851</v>
@@ -10875,12 +10881,12 @@
         <v>872</v>
       </c>
       <c r="B457" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B458" t="s">
         <v>874</v>
@@ -10995,15 +11001,15 @@
         <v>901</v>
       </c>
       <c r="B472" t="s">
-        <v>162</v>
+        <v>902</v>
       </c>
     </row>
     <row r="473" spans="1:2">
       <c r="A473" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B473" t="s">
-        <v>903</v>
+        <v>162</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -11099,20 +11105,20 @@
         <v>926</v>
       </c>
       <c r="B485" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B486" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B487" t="s">
         <v>929</v>
@@ -11347,12 +11353,12 @@
         <v>986</v>
       </c>
       <c r="B516" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B517" t="s">
         <v>988</v>
@@ -11515,12 +11521,12 @@
         <v>1027</v>
       </c>
       <c r="B537" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B538" t="s">
         <v>1029</v>
@@ -11555,12 +11561,12 @@
         <v>1036</v>
       </c>
       <c r="B542" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B543" t="s">
         <v>1038</v>
@@ -11787,12 +11793,12 @@
         <v>1093</v>
       </c>
       <c r="B571" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="572" spans="1:2">
       <c r="A572" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B572" t="s">
         <v>1095</v>
@@ -11859,12 +11865,12 @@
         <v>1110</v>
       </c>
       <c r="B580" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B581" t="s">
         <v>1112</v>
@@ -12027,12 +12033,12 @@
         <v>1151</v>
       </c>
       <c r="B601" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B602" t="s">
         <v>1153</v>
@@ -12211,12 +12217,12 @@
         <v>1196</v>
       </c>
       <c r="B624" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B625" t="s">
         <v>1198</v>
@@ -12235,23 +12241,23 @@
         <v>1201</v>
       </c>
       <c r="B627" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B628" t="s">
-        <v>874</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B629" t="s">
-        <v>1204</v>
+        <v>876</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -12395,12 +12401,12 @@
         <v>1239</v>
       </c>
       <c r="B647" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B648" t="s">
         <v>1241</v>
@@ -12491,12 +12497,12 @@
         <v>1262</v>
       </c>
       <c r="B659" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B660" t="s">
         <v>1264</v>
@@ -12683,12 +12689,12 @@
         <v>1309</v>
       </c>
       <c r="B683" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B684" t="s">
         <v>1311</v>
@@ -12747,12 +12753,12 @@
         <v>1324</v>
       </c>
       <c r="B691" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B692" t="s">
         <v>1326</v>
@@ -12883,12 +12889,12 @@
         <v>1357</v>
       </c>
       <c r="B708" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B709" t="s">
         <v>1359</v>
@@ -12971,12 +12977,12 @@
         <v>1378</v>
       </c>
       <c r="B719" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B720" t="s">
         <v>1380</v>
@@ -13131,12 +13137,12 @@
         <v>1417</v>
       </c>
       <c r="B739" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B740" t="s">
         <v>1419</v>
@@ -13587,20 +13593,20 @@
         <v>1530</v>
       </c>
       <c r="B796" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B797" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B798" t="s">
         <v>1533</v>
@@ -13611,12 +13617,12 @@
         <v>1534</v>
       </c>
       <c r="B799" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B800" t="s">
         <v>1536</v>
@@ -13643,12 +13649,12 @@
         <v>1541</v>
       </c>
       <c r="B803" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B804" t="s">
         <v>1543</v>
@@ -13675,12 +13681,12 @@
         <v>1548</v>
       </c>
       <c r="B807" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B808" t="s">
         <v>1550</v>
@@ -13691,12 +13697,12 @@
         <v>1551</v>
       </c>
       <c r="B809" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B810" t="s">
         <v>1553</v>
@@ -13939,36 +13945,36 @@
         <v>1612</v>
       </c>
       <c r="B840" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B841" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B842" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B843" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B844" t="s">
         <v>1617</v>
@@ -14011,12 +14017,12 @@
         <v>1626</v>
       </c>
       <c r="B849" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B850" t="s">
         <v>1628</v>
@@ -14275,12 +14281,12 @@
         <v>1691</v>
       </c>
       <c r="B882" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B883" t="s">
         <v>1693</v>
@@ -14347,20 +14353,20 @@
         <v>1708</v>
       </c>
       <c r="B891" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B892" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B893" t="s">
         <v>1711</v>
@@ -14403,12 +14409,12 @@
         <v>1720</v>
       </c>
       <c r="B898" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B899" t="s">
         <v>1722</v>
@@ -14539,20 +14545,20 @@
         <v>1753</v>
       </c>
       <c r="B915" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B916" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B917" t="s">
         <v>1756</v>
@@ -14563,20 +14569,20 @@
         <v>1757</v>
       </c>
       <c r="B918" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B919" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B920" t="s">
         <v>1760</v>
@@ -14587,12 +14593,12 @@
         <v>1761</v>
       </c>
       <c r="B921" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="B922" t="s">
         <v>1763</v>
@@ -14643,12 +14649,12 @@
         <v>1774</v>
       </c>
       <c r="B928" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B929" t="s">
         <v>1776</v>
@@ -14723,12 +14729,12 @@
         <v>1793</v>
       </c>
       <c r="B938" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B939" t="s">
         <v>1795</v>
@@ -14835,12 +14841,12 @@
         <v>1820</v>
       </c>
       <c r="B952" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B953" t="s">
         <v>1822</v>
@@ -15171,12 +15177,12 @@
         <v>1903</v>
       </c>
       <c r="B994" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B995" t="s">
         <v>1905</v>
@@ -15403,12 +15409,12 @@
         <v>1960</v>
       </c>
       <c r="B1023" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="B1024" t="s">
         <v>1962</v>
@@ -15451,12 +15457,12 @@
         <v>1971</v>
       </c>
       <c r="B1029" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="B1030" t="s">
         <v>1973</v>
@@ -15539,12 +15545,12 @@
         <v>1992</v>
       </c>
       <c r="B1040" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="B1041" t="s">
         <v>1994</v>
@@ -15907,12 +15913,12 @@
         <v>2083</v>
       </c>
       <c r="B1086" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="B1087" t="s">
         <v>2085</v>
@@ -16123,12 +16129,12 @@
         <v>2136</v>
       </c>
       <c r="B1113" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="B1114" t="s">
         <v>2138</v>
@@ -16195,12 +16201,12 @@
         <v>2153</v>
       </c>
       <c r="B1122" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="B1123" t="s">
         <v>2155</v>
@@ -16419,12 +16425,12 @@
         <v>2208</v>
       </c>
       <c r="B1150" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="B1151" t="s">
         <v>2210</v>
@@ -16547,12 +16553,12 @@
         <v>2239</v>
       </c>
       <c r="B1166" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="B1167" t="s">
         <v>2241</v>
@@ -16571,12 +16577,12 @@
         <v>2244</v>
       </c>
       <c r="B1169" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="B1170" t="s">
         <v>2246</v>
@@ -16595,12 +16601,12 @@
         <v>2249</v>
       </c>
       <c r="B1172" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="B1173" t="s">
         <v>2251</v>
@@ -16611,12 +16617,12 @@
         <v>2252</v>
       </c>
       <c r="B1174" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="B1175" t="s">
         <v>2254</v>
@@ -16659,12 +16665,12 @@
         <v>2263</v>
       </c>
       <c r="B1180" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="B1181" t="s">
         <v>2265</v>
@@ -16675,12 +16681,12 @@
         <v>2266</v>
       </c>
       <c r="B1182" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="B1183" t="s">
         <v>2268</v>
@@ -16739,19 +16745,27 @@
         <v>2281</v>
       </c>
       <c r="B1190" t="s">
-        <v>2142</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="B1191" t="s">
-        <v>2283</v>
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:2">
+      <c r="A1192" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>2285</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1191"/>
+  <autoFilter ref="A1:B1192"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ko/headTags.xlsx
+++ b/lang/ko/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1193</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2288">
   <si>
     <t>en</t>
   </si>
@@ -2393,6 +2393,12 @@
   </si>
   <si>
     <t>글꼴(주황색)</t>
+  </si>
+  <si>
+    <t>Font (Pale Oak)</t>
+  </si>
+  <si>
+    <t>글꼴 (Pale Oak)</t>
   </si>
   <si>
     <t>Font (Pink)</t>
@@ -7221,7 +7227,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1192"/>
+  <dimension ref="A1:B1193"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -10705,12 +10711,12 @@
         <v>832</v>
       </c>
       <c r="B435" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B436" t="s">
         <v>834</v>
@@ -10729,12 +10735,12 @@
         <v>837</v>
       </c>
       <c r="B438" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B439" t="s">
         <v>839</v>
@@ -10777,12 +10783,12 @@
         <v>848</v>
       </c>
       <c r="B444" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="445" spans="1:2">
       <c r="A445" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B445" t="s">
         <v>850</v>
@@ -10793,12 +10799,12 @@
         <v>851</v>
       </c>
       <c r="B446" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B447" t="s">
         <v>853</v>
@@ -10889,12 +10895,12 @@
         <v>874</v>
       </c>
       <c r="B458" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B459" t="s">
         <v>876</v>
@@ -11009,15 +11015,15 @@
         <v>903</v>
       </c>
       <c r="B473" t="s">
-        <v>162</v>
+        <v>904</v>
       </c>
     </row>
     <row r="474" spans="1:2">
       <c r="A474" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B474" t="s">
-        <v>905</v>
+        <v>162</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -11113,20 +11119,20 @@
         <v>928</v>
       </c>
       <c r="B486" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B487" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B488" t="s">
         <v>931</v>
@@ -11361,12 +11367,12 @@
         <v>988</v>
       </c>
       <c r="B517" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B518" t="s">
         <v>990</v>
@@ -11529,12 +11535,12 @@
         <v>1029</v>
       </c>
       <c r="B538" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B539" t="s">
         <v>1031</v>
@@ -11569,12 +11575,12 @@
         <v>1038</v>
       </c>
       <c r="B543" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B544" t="s">
         <v>1040</v>
@@ -11801,12 +11807,12 @@
         <v>1095</v>
       </c>
       <c r="B572" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B573" t="s">
         <v>1097</v>
@@ -11873,12 +11879,12 @@
         <v>1112</v>
       </c>
       <c r="B581" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B582" t="s">
         <v>1114</v>
@@ -12041,12 +12047,12 @@
         <v>1153</v>
       </c>
       <c r="B602" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B603" t="s">
         <v>1155</v>
@@ -12225,12 +12231,12 @@
         <v>1198</v>
       </c>
       <c r="B625" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B626" t="s">
         <v>1200</v>
@@ -12249,23 +12255,23 @@
         <v>1203</v>
       </c>
       <c r="B628" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B629" t="s">
-        <v>876</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B630" t="s">
-        <v>1206</v>
+        <v>878</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -12409,12 +12415,12 @@
         <v>1241</v>
       </c>
       <c r="B648" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B649" t="s">
         <v>1243</v>
@@ -12505,12 +12511,12 @@
         <v>1264</v>
       </c>
       <c r="B660" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B661" t="s">
         <v>1266</v>
@@ -12697,12 +12703,12 @@
         <v>1311</v>
       </c>
       <c r="B684" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B685" t="s">
         <v>1313</v>
@@ -12761,12 +12767,12 @@
         <v>1326</v>
       </c>
       <c r="B692" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B693" t="s">
         <v>1328</v>
@@ -12897,12 +12903,12 @@
         <v>1359</v>
       </c>
       <c r="B709" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B710" t="s">
         <v>1361</v>
@@ -12985,12 +12991,12 @@
         <v>1380</v>
       </c>
       <c r="B720" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B721" t="s">
         <v>1382</v>
@@ -13145,12 +13151,12 @@
         <v>1419</v>
       </c>
       <c r="B740" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B741" t="s">
         <v>1421</v>
@@ -13601,20 +13607,20 @@
         <v>1532</v>
       </c>
       <c r="B797" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B798" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B799" t="s">
         <v>1535</v>
@@ -13625,12 +13631,12 @@
         <v>1536</v>
       </c>
       <c r="B800" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B801" t="s">
         <v>1538</v>
@@ -13657,12 +13663,12 @@
         <v>1543</v>
       </c>
       <c r="B804" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B805" t="s">
         <v>1545</v>
@@ -13689,12 +13695,12 @@
         <v>1550</v>
       </c>
       <c r="B808" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B809" t="s">
         <v>1552</v>
@@ -13705,12 +13711,12 @@
         <v>1553</v>
       </c>
       <c r="B810" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B811" t="s">
         <v>1555</v>
@@ -13953,36 +13959,36 @@
         <v>1614</v>
       </c>
       <c r="B841" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B842" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B843" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B844" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B845" t="s">
         <v>1619</v>
@@ -14025,12 +14031,12 @@
         <v>1628</v>
       </c>
       <c r="B850" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B851" t="s">
         <v>1630</v>
@@ -14289,12 +14295,12 @@
         <v>1693</v>
       </c>
       <c r="B883" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B884" t="s">
         <v>1695</v>
@@ -14361,20 +14367,20 @@
         <v>1710</v>
       </c>
       <c r="B892" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B893" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B894" t="s">
         <v>1713</v>
@@ -14417,12 +14423,12 @@
         <v>1722</v>
       </c>
       <c r="B899" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B900" t="s">
         <v>1724</v>
@@ -14553,20 +14559,20 @@
         <v>1755</v>
       </c>
       <c r="B916" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="B917" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="B918" t="s">
         <v>1758</v>
@@ -14577,20 +14583,20 @@
         <v>1759</v>
       </c>
       <c r="B919" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B920" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="B921" t="s">
         <v>1762</v>
@@ -14601,12 +14607,12 @@
         <v>1763</v>
       </c>
       <c r="B922" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="B923" t="s">
         <v>1765</v>
@@ -14657,12 +14663,12 @@
         <v>1776</v>
       </c>
       <c r="B929" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B930" t="s">
         <v>1778</v>
@@ -14737,12 +14743,12 @@
         <v>1795</v>
       </c>
       <c r="B939" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B940" t="s">
         <v>1797</v>
@@ -14849,12 +14855,12 @@
         <v>1822</v>
       </c>
       <c r="B953" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B954" t="s">
         <v>1824</v>
@@ -15185,12 +15191,12 @@
         <v>1905</v>
       </c>
       <c r="B995" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B996" t="s">
         <v>1907</v>
@@ -15417,12 +15423,12 @@
         <v>1962</v>
       </c>
       <c r="B1024" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="B1025" t="s">
         <v>1964</v>
@@ -15465,12 +15471,12 @@
         <v>1973</v>
       </c>
       <c r="B1030" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B1031" t="s">
         <v>1975</v>
@@ -15553,12 +15559,12 @@
         <v>1994</v>
       </c>
       <c r="B1041" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="B1042" t="s">
         <v>1996</v>
@@ -15921,12 +15927,12 @@
         <v>2085</v>
       </c>
       <c r="B1087" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="B1088" t="s">
         <v>2087</v>
@@ -16137,12 +16143,12 @@
         <v>2138</v>
       </c>
       <c r="B1114" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="B1115" t="s">
         <v>2140</v>
@@ -16209,12 +16215,12 @@
         <v>2155</v>
       </c>
       <c r="B1123" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="B1124" t="s">
         <v>2157</v>
@@ -16433,12 +16439,12 @@
         <v>2210</v>
       </c>
       <c r="B1151" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="B1152" t="s">
         <v>2212</v>
@@ -16561,12 +16567,12 @@
         <v>2241</v>
       </c>
       <c r="B1167" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="B1168" t="s">
         <v>2243</v>
@@ -16585,12 +16591,12 @@
         <v>2246</v>
       </c>
       <c r="B1170" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="B1171" t="s">
         <v>2248</v>
@@ -16609,12 +16615,12 @@
         <v>2251</v>
       </c>
       <c r="B1173" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="B1174" t="s">
         <v>2253</v>
@@ -16625,12 +16631,12 @@
         <v>2254</v>
       </c>
       <c r="B1175" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="B1176" t="s">
         <v>2256</v>
@@ -16673,12 +16679,12 @@
         <v>2265</v>
       </c>
       <c r="B1181" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B1182" t="s">
         <v>2267</v>
@@ -16689,12 +16695,12 @@
         <v>2268</v>
       </c>
       <c r="B1183" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="B1184" t="s">
         <v>2270</v>
@@ -16753,19 +16759,27 @@
         <v>2283</v>
       </c>
       <c r="B1191" t="s">
-        <v>2144</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="B1192" t="s">
-        <v>2285</v>
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:2">
+      <c r="A1193" t="s">
+        <v>2286</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>2287</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1192"/>
+  <autoFilter ref="A1:B1193"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
